--- a/請求書・見積書/かもめ-フォーラム(Yokusuru)/見積書・請求書テンプレート.xlsx
+++ b/請求書・見積書/かもめ-フォーラム(Yokusuru)/見積書・請求書テンプレート.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10110"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chikakokunugi/Documents/GitHub/private/請求書・見積書/かもめ-フォーラム(Yokusuru)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F80161B7-8CBE-0A48-B0BC-5612616EB415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{44911E82-1EE1-804A-A9D7-2AA09480F75D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35680" yWindow="-19360" windowWidth="27640" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-29580" yWindow="-21120" windowWidth="38400" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="請求書" sheetId="1" r:id="rId1"/>
@@ -26,6 +26,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="3">発注書!$A$1:$H$35</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -538,21 +539,12 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>新神戸ウェルネスクリニック美容皮膚科のHP更新作業</t>
-    <rPh sb="2" eb="4">
-      <t xml:space="preserve">シカ </t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t xml:space="preserve">サマ </t>
-    </rPh>
+    <t>WEBサイトの修正・更新作業 (対象サイト：https://www.ilink-kaitori.net/、https://www.esthe-kaitori.com/、https://www.drone-kaitori.com/）</t>
     <rPh sb="7" eb="9">
-      <t>サイヨウ</t>
-    </rPh>
-    <rPh sb="19" eb="22">
-      <t>コウゾウクミコミ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>セッテイ</t>
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>コウシンサグ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -1022,7 +1014,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="38" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1145,12 +1137,57 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="42" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="22" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1160,57 +1197,15 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="22" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="42" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="42" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="5" fontId="18" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1241,8 +1236,8 @@
     <xf numFmtId="31" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1670,26 +1665,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" customHeight="1">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
     </row>
     <row r="2" spans="1:8" ht="23.25" customHeight="1">
-      <c r="A2" s="69"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
+      <c r="A2" s="56"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
     </row>
     <row r="3" spans="1:8" ht="10" customHeight="1">
       <c r="A3" s="2"/>
@@ -1712,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="46">
-        <v>46008</v>
+        <v>46053</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16" customHeight="1">
@@ -1749,22 +1744,22 @@
       <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:8" ht="29" customHeight="1">
-      <c r="A8" s="58" t="s">
+      <c r="A8" s="73" t="s">
         <v>58</v>
       </c>
-      <c r="B8" s="59"/>
-      <c r="C8" s="59"/>
-      <c r="D8" s="59"/>
+      <c r="B8" s="74"/>
+      <c r="C8" s="74"/>
+      <c r="D8" s="74"/>
       <c r="E8" s="2"/>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:8" ht="23" customHeight="1" thickBot="1">
-      <c r="A9" s="60"/>
-      <c r="B9" s="60"/>
-      <c r="C9" s="60"/>
-      <c r="D9" s="60"/>
+      <c r="A9" s="75"/>
+      <c r="B9" s="75"/>
+      <c r="C9" s="75"/>
+      <c r="D9" s="75"/>
       <c r="E9" s="2"/>
       <c r="F9" s="5"/>
       <c r="G9" s="5" t="s">
@@ -1815,15 +1810,15 @@
       <c r="H13" s="2"/>
     </row>
     <row r="14" spans="1:8" s="1" customFormat="1" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A14" s="68" t="s">
+      <c r="A14" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="68"/>
-      <c r="C14" s="67">
+      <c r="B14" s="72"/>
+      <c r="C14" s="71">
         <f>G32</f>
-        <v>9000</v>
-      </c>
-      <c r="D14" s="67"/>
+        <v>6000</v>
+      </c>
+      <c r="D14" s="71"/>
       <c r="E14" s="10"/>
       <c r="F14" s="11"/>
       <c r="G14" s="11"/>
@@ -1840,13 +1835,13 @@
       <c r="H15" s="2"/>
     </row>
     <row r="16" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A16" s="65" t="s">
+      <c r="A16" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="66"/>
-      <c r="C16" s="66"/>
-      <c r="D16" s="66"/>
-      <c r="E16" s="66"/>
+      <c r="B16" s="70"/>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
       <c r="F16" s="44" t="s">
         <v>1</v>
       </c>
@@ -1857,23 +1852,23 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="22" customHeight="1">
-      <c r="A17" s="61" t="s">
+    <row r="17" spans="1:8" ht="63" customHeight="1">
+      <c r="A17" s="89" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="62"/>
-      <c r="C17" s="62"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="62"/>
+      <c r="B17" s="68"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
       <c r="F17" s="35">
         <v>1</v>
       </c>
       <c r="G17" s="36">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="H17" s="37">
         <f t="shared" ref="H17" si="0">F17*G17</f>
-        <v>9000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="22" customHeight="1">
@@ -1987,17 +1982,17 @@
       <c r="H28" s="40"/>
     </row>
     <row r="29" spans="1:8" ht="22" customHeight="1">
-      <c r="A29" s="74"/>
-      <c r="B29" s="75"/>
-      <c r="C29" s="75"/>
-      <c r="D29" s="75"/>
-      <c r="E29" s="75"/>
+      <c r="A29" s="61"/>
+      <c r="B29" s="62"/>
+      <c r="C29" s="62"/>
+      <c r="D29" s="62"/>
+      <c r="E29" s="62"/>
       <c r="F29" s="41"/>
       <c r="G29" s="42"/>
       <c r="H29" s="43"/>
     </row>
     <row r="30" spans="1:8" ht="28.5" customHeight="1">
-      <c r="A30" s="56" t="s">
+      <c r="A30" s="65" t="s">
         <v>18</v>
       </c>
       <c r="B30" s="5" t="s">
@@ -2007,11 +2002,11 @@
       <c r="D30" s="5"/>
       <c r="E30" s="2"/>
       <c r="F30" s="19"/>
-      <c r="G30" s="88"/>
-      <c r="H30" s="88"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
     </row>
     <row r="31" spans="1:8" ht="28.5" customHeight="1" thickBot="1">
-      <c r="A31" s="57"/>
+      <c r="A31" s="66"/>
       <c r="B31" s="48" t="s">
         <v>52</v>
       </c>
@@ -2021,29 +2016,29 @@
       <c r="F31" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="G31" s="70">
-        <v>9000</v>
-      </c>
-      <c r="H31" s="70"/>
+      <c r="G31" s="58">
+        <v>6000</v>
+      </c>
+      <c r="H31" s="58"/>
     </row>
     <row r="32" spans="1:8" ht="28.5" customHeight="1" thickBot="1">
       <c r="A32" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="B32" s="73">
-        <v>46081</v>
-      </c>
-      <c r="C32" s="73"/>
-      <c r="D32" s="73"/>
+      <c r="B32" s="60">
+        <v>46112</v>
+      </c>
+      <c r="C32" s="60"/>
+      <c r="D32" s="60"/>
       <c r="E32" s="2"/>
       <c r="F32" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="G32" s="72">
+      <c r="G32" s="59">
         <f>G30+G31</f>
-        <v>9000</v>
-      </c>
-      <c r="H32" s="72"/>
+        <v>6000</v>
+      </c>
+      <c r="H32" s="59"/>
     </row>
     <row r="33" spans="1:8" ht="22" customHeight="1">
       <c r="A33" s="12"/>
@@ -2092,6 +2087,13 @@
     <row r="39" spans="1:8" ht="22" customHeight="1"/>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A8:D9"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A14:B14"/>
     <mergeCell ref="A1:H2"/>
     <mergeCell ref="G30:H30"/>
     <mergeCell ref="G31:H31"/>
@@ -2108,13 +2110,6 @@
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A19:E19"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A8:D9"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1"/>
@@ -2141,26 +2136,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" customHeight="1">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
     </row>
     <row r="2" spans="1:8" ht="23.25" customHeight="1">
-      <c r="A2" s="69"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
+      <c r="A2" s="56"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
     </row>
     <row r="3" spans="1:8" ht="10" customHeight="1">
       <c r="A3" s="2"/>
@@ -2223,22 +2218,22 @@
       <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:8" ht="18.75" customHeight="1">
-      <c r="A8" s="58" t="s">
+      <c r="A8" s="73" t="s">
         <v>58</v>
       </c>
-      <c r="B8" s="59"/>
-      <c r="C8" s="59"/>
-      <c r="D8" s="59"/>
+      <c r="B8" s="74"/>
+      <c r="C8" s="74"/>
+      <c r="D8" s="74"/>
       <c r="E8" s="2"/>
       <c r="F8" s="34"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:8" ht="29" customHeight="1" thickBot="1">
-      <c r="A9" s="60"/>
-      <c r="B9" s="60"/>
-      <c r="C9" s="60"/>
-      <c r="D9" s="60"/>
+      <c r="A9" s="75"/>
+      <c r="B9" s="75"/>
+      <c r="C9" s="75"/>
+      <c r="D9" s="75"/>
       <c r="E9" s="2"/>
       <c r="F9" s="5" t="s">
         <v>48</v>
@@ -2295,15 +2290,15 @@
       <c r="H13" s="2"/>
     </row>
     <row r="14" spans="1:8" s="1" customFormat="1" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A14" s="68" t="s">
+      <c r="A14" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="68"/>
-      <c r="C14" s="67">
+      <c r="B14" s="72"/>
+      <c r="C14" s="71">
         <f>G32</f>
         <v>3300</v>
       </c>
-      <c r="D14" s="67"/>
+      <c r="D14" s="71"/>
       <c r="E14" s="10"/>
       <c r="F14" s="11"/>
       <c r="G14" s="11"/>
@@ -2320,13 +2315,13 @@
       <c r="H15" s="2"/>
     </row>
     <row r="16" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A16" s="65" t="s">
+      <c r="A16" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="66"/>
-      <c r="C16" s="66"/>
-      <c r="D16" s="66"/>
-      <c r="E16" s="66"/>
+      <c r="B16" s="70"/>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
       <c r="F16" s="44" t="s">
         <v>1</v>
       </c>
@@ -2338,13 +2333,13 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="22" customHeight="1">
-      <c r="A17" s="61" t="s">
+      <c r="A17" s="67" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="62"/>
-      <c r="C17" s="62"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="62"/>
+      <c r="B17" s="68"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
       <c r="F17" s="35">
         <v>1</v>
       </c>
@@ -2467,11 +2462,11 @@
       <c r="H28" s="40"/>
     </row>
     <row r="29" spans="1:8" ht="22" customHeight="1">
-      <c r="A29" s="74"/>
-      <c r="B29" s="75"/>
-      <c r="C29" s="75"/>
-      <c r="D29" s="75"/>
-      <c r="E29" s="75"/>
+      <c r="A29" s="61"/>
+      <c r="B29" s="62"/>
+      <c r="C29" s="62"/>
+      <c r="D29" s="62"/>
+      <c r="E29" s="62"/>
       <c r="F29" s="41"/>
       <c r="G29" s="42"/>
       <c r="H29" s="43"/>
@@ -2485,11 +2480,11 @@
       <c r="F30" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="G30" s="70">
+      <c r="G30" s="58">
         <f>SUM(H17:H21)</f>
         <v>3000</v>
       </c>
-      <c r="H30" s="70"/>
+      <c r="H30" s="58"/>
     </row>
     <row r="31" spans="1:8" ht="28.5" customHeight="1" thickBot="1">
       <c r="A31" s="50" t="s">
@@ -2502,30 +2497,30 @@
       <c r="F31" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="G31" s="71">
+      <c r="G31" s="76">
         <f>G30*0.1</f>
         <v>300</v>
       </c>
-      <c r="H31" s="71"/>
+      <c r="H31" s="76"/>
     </row>
     <row r="32" spans="1:8" ht="28.5" customHeight="1" thickBot="1">
       <c r="A32" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="B32" s="73">
+      <c r="B32" s="60">
         <v>46022</v>
       </c>
-      <c r="C32" s="73"/>
-      <c r="D32" s="73"/>
+      <c r="C32" s="60"/>
+      <c r="D32" s="60"/>
       <c r="E32" s="2"/>
       <c r="F32" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="G32" s="72">
+      <c r="G32" s="59">
         <f>G30+G31</f>
         <v>3300</v>
       </c>
-      <c r="H32" s="72"/>
+      <c r="H32" s="59"/>
     </row>
     <row r="33" spans="1:8" ht="22" customHeight="1">
       <c r="A33" s="12"/>
@@ -2574,12 +2569,6 @@
     <row r="39" spans="1:8" ht="22" customHeight="1"/>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A17:E17"/>
     <mergeCell ref="G31:H31"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="G32:H32"/>
@@ -2596,6 +2585,12 @@
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A17:E17"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1"/>
@@ -2619,26 +2614,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" customHeight="1">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
     </row>
     <row r="2" spans="1:8" ht="23.25" customHeight="1">
-      <c r="A2" s="69"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
+      <c r="A2" s="56"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
     </row>
     <row r="3" spans="1:8" ht="10" customHeight="1">
       <c r="A3" s="2"/>
@@ -2699,12 +2694,12 @@
       <c r="E7" s="8"/>
     </row>
     <row r="8" spans="1:8" ht="18.75" customHeight="1">
-      <c r="A8" s="59" t="s">
+      <c r="A8" s="74" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="59"/>
-      <c r="C8" s="59"/>
-      <c r="D8" s="59"/>
+      <c r="B8" s="74"/>
+      <c r="C8" s="74"/>
+      <c r="D8" s="74"/>
       <c r="E8" s="2"/>
       <c r="F8" s="34" t="s">
         <v>8</v>
@@ -2713,10 +2708,10 @@
       <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:8" ht="18.75" customHeight="1" thickBot="1">
-      <c r="A9" s="60"/>
-      <c r="B9" s="60"/>
-      <c r="C9" s="60"/>
-      <c r="D9" s="60"/>
+      <c r="A9" s="75"/>
+      <c r="B9" s="75"/>
+      <c r="C9" s="75"/>
+      <c r="D9" s="75"/>
       <c r="E9" s="2"/>
       <c r="F9" s="5" t="s">
         <v>11</v>
@@ -2777,15 +2772,15 @@
       <c r="H13" s="2"/>
     </row>
     <row r="14" spans="1:8" s="1" customFormat="1" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A14" s="68" t="s">
+      <c r="A14" s="72" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="68"/>
-      <c r="C14" s="67">
+      <c r="B14" s="72"/>
+      <c r="C14" s="71">
         <f>G32</f>
         <v>896500</v>
       </c>
-      <c r="D14" s="67"/>
+      <c r="D14" s="71"/>
       <c r="E14" s="10"/>
       <c r="F14" s="11"/>
       <c r="G14" s="11"/>
@@ -2802,13 +2797,13 @@
       <c r="H15" s="2"/>
     </row>
     <row r="16" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A16" s="65" t="s">
+      <c r="A16" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="66"/>
-      <c r="C16" s="66"/>
-      <c r="D16" s="66"/>
-      <c r="E16" s="66"/>
+      <c r="B16" s="70"/>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
       <c r="F16" s="44" t="s">
         <v>1</v>
       </c>
@@ -2820,13 +2815,13 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="22" customHeight="1">
-      <c r="A17" s="61" t="s">
+      <c r="A17" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="62"/>
-      <c r="C17" s="62"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="62"/>
+      <c r="B17" s="68"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
       <c r="F17" s="35">
         <v>100</v>
       </c>
@@ -2985,11 +2980,11 @@
       <c r="H28" s="40"/>
     </row>
     <row r="29" spans="1:8" ht="22" customHeight="1">
-      <c r="A29" s="74"/>
-      <c r="B29" s="75"/>
-      <c r="C29" s="75"/>
-      <c r="D29" s="75"/>
-      <c r="E29" s="75"/>
+      <c r="A29" s="61"/>
+      <c r="B29" s="62"/>
+      <c r="C29" s="62"/>
+      <c r="D29" s="62"/>
+      <c r="E29" s="62"/>
       <c r="F29" s="41"/>
       <c r="G29" s="42"/>
       <c r="H29" s="43"/>
@@ -3003,11 +2998,11 @@
       <c r="F30" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="G30" s="70">
+      <c r="G30" s="58">
         <f>SUM(H17:H21)</f>
         <v>815000</v>
       </c>
-      <c r="H30" s="70"/>
+      <c r="H30" s="58"/>
     </row>
     <row r="31" spans="1:8" ht="28.5" customHeight="1" thickBot="1">
       <c r="A31" s="16"/>
@@ -3018,11 +3013,11 @@
       <c r="F31" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="G31" s="71">
+      <c r="G31" s="76">
         <f>G30*0.1</f>
         <v>81500</v>
       </c>
-      <c r="H31" s="71"/>
+      <c r="H31" s="76"/>
     </row>
     <row r="32" spans="1:8" ht="28.5" customHeight="1" thickBot="1">
       <c r="A32" s="12"/>
@@ -3033,11 +3028,11 @@
       <c r="F32" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="G32" s="76">
+      <c r="G32" s="78">
         <f>G30+G31</f>
         <v>896500</v>
       </c>
-      <c r="H32" s="76"/>
+      <c r="H32" s="78"/>
     </row>
     <row r="33" spans="1:8" ht="22" customHeight="1">
       <c r="A33" s="20" t="s">
@@ -3075,12 +3070,6 @@
     <row r="38" spans="1:8" ht="22" customHeight="1"/>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="A16:E16"/>
     <mergeCell ref="G30:H30"/>
     <mergeCell ref="G31:H31"/>
     <mergeCell ref="G32:H32"/>
@@ -3097,6 +3086,12 @@
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A16:E16"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1"/>
@@ -3120,26 +3115,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21" customHeight="1">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
     </row>
     <row r="2" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A2" s="69"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
+      <c r="A2" s="56"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
     </row>
     <row r="3" spans="1:9" ht="10" customHeight="1">
       <c r="A3" s="2"/>
@@ -3200,12 +3195,12 @@
       <c r="E7" s="8"/>
     </row>
     <row r="8" spans="1:9" ht="18.75" customHeight="1">
-      <c r="A8" s="59" t="s">
+      <c r="A8" s="74" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="59"/>
-      <c r="C8" s="59"/>
-      <c r="D8" s="59"/>
+      <c r="B8" s="74"/>
+      <c r="C8" s="74"/>
+      <c r="D8" s="74"/>
       <c r="E8" s="2"/>
       <c r="F8" s="34" t="s">
         <v>8</v>
@@ -3215,10 +3210,10 @@
       <c r="I8" s="54"/>
     </row>
     <row r="9" spans="1:9" ht="18.75" customHeight="1" thickBot="1">
-      <c r="A9" s="60"/>
-      <c r="B9" s="60"/>
-      <c r="C9" s="60"/>
-      <c r="D9" s="60"/>
+      <c r="A9" s="75"/>
+      <c r="B9" s="75"/>
+      <c r="C9" s="75"/>
+      <c r="D9" s="75"/>
       <c r="E9" s="2"/>
       <c r="F9" s="5" t="s">
         <v>11</v>
@@ -3282,15 +3277,15 @@
       <c r="H13" s="2"/>
     </row>
     <row r="14" spans="1:9" s="1" customFormat="1" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A14" s="68" t="s">
+      <c r="A14" s="72" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="68"/>
-      <c r="C14" s="67">
+      <c r="B14" s="72"/>
+      <c r="C14" s="71">
         <f>G32</f>
         <v>896500</v>
       </c>
-      <c r="D14" s="67"/>
+      <c r="D14" s="71"/>
       <c r="E14" s="10"/>
       <c r="F14" s="11"/>
       <c r="G14" s="53"/>
@@ -3307,13 +3302,13 @@
       <c r="H15" s="2"/>
     </row>
     <row r="16" spans="1:9" ht="24.75" customHeight="1">
-      <c r="A16" s="65" t="s">
+      <c r="A16" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="66"/>
-      <c r="C16" s="66"/>
-      <c r="D16" s="66"/>
-      <c r="E16" s="66"/>
+      <c r="B16" s="70"/>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
       <c r="F16" s="44" t="s">
         <v>1</v>
       </c>
@@ -3325,13 +3320,13 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="22" customHeight="1">
-      <c r="A17" s="61" t="s">
+      <c r="A17" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="62"/>
-      <c r="C17" s="62"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="62"/>
+      <c r="B17" s="68"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
       <c r="F17" s="35">
         <v>100</v>
       </c>
@@ -3490,11 +3485,11 @@
       <c r="H28" s="40"/>
     </row>
     <row r="29" spans="1:8" ht="22" customHeight="1">
-      <c r="A29" s="74"/>
-      <c r="B29" s="75"/>
-      <c r="C29" s="75"/>
-      <c r="D29" s="75"/>
-      <c r="E29" s="75"/>
+      <c r="A29" s="61"/>
+      <c r="B29" s="62"/>
+      <c r="C29" s="62"/>
+      <c r="D29" s="62"/>
+      <c r="E29" s="62"/>
       <c r="F29" s="41"/>
       <c r="G29" s="42"/>
       <c r="H29" s="43"/>
@@ -3508,11 +3503,11 @@
       <c r="F30" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="G30" s="70">
+      <c r="G30" s="58">
         <f>SUM(H17:H21)</f>
         <v>815000</v>
       </c>
-      <c r="H30" s="70"/>
+      <c r="H30" s="58"/>
     </row>
     <row r="31" spans="1:8" ht="28.5" customHeight="1" thickBot="1">
       <c r="A31" s="12"/>
@@ -3523,11 +3518,11 @@
       <c r="F31" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="G31" s="71">
+      <c r="G31" s="76">
         <f>G30*0.1</f>
         <v>81500</v>
       </c>
-      <c r="H31" s="71"/>
+      <c r="H31" s="76"/>
     </row>
     <row r="32" spans="1:8" ht="28.5" customHeight="1" thickBot="1">
       <c r="A32" s="12"/>
@@ -3538,11 +3533,11 @@
       <c r="F32" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="G32" s="76">
+      <c r="G32" s="78">
         <f>G30+G31</f>
         <v>896500</v>
       </c>
-      <c r="H32" s="76"/>
+      <c r="H32" s="78"/>
     </row>
     <row r="33" spans="1:8" ht="22" customHeight="1">
       <c r="A33" s="20" t="s">
@@ -3580,6 +3575,16 @@
     <row r="38" spans="1:8" ht="22" customHeight="1"/>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:E28"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="A1:H2"/>
     <mergeCell ref="A8:D9"/>
@@ -3592,16 +3597,6 @@
     <mergeCell ref="A19:E19"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A28:E28"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1"/>
@@ -3622,55 +3617,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20" customHeight="1">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="56" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="69"/>
-      <c r="J1" s="69"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
     </row>
     <row r="2" spans="1:10" ht="20" customHeight="1">
-      <c r="A2" s="69"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
+      <c r="A2" s="56"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
     </row>
     <row r="3" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="85">
+      <c r="I3" s="86">
         <v>123456</v>
       </c>
-      <c r="J3" s="85"/>
+      <c r="J3" s="86"/>
     </row>
     <row r="4" spans="1:10" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A4" s="81"/>
-      <c r="B4" s="81"/>
-      <c r="C4" s="81"/>
-      <c r="D4" s="81"/>
-      <c r="E4" s="81"/>
+      <c r="A4" s="82"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -3695,12 +3690,12 @@
       <c r="C6" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="79">
+      <c r="D6" s="80">
         <v>123456</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79"/>
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80"/>
       <c r="H6" s="30"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
@@ -3709,35 +3704,35 @@
       <c r="C7" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="86"/>
-      <c r="E7" s="86"/>
-      <c r="F7" s="86"/>
-      <c r="G7" s="86"/>
-      <c r="H7" s="86"/>
+      <c r="D7" s="87"/>
+      <c r="E7" s="87"/>
+      <c r="F7" s="87"/>
+      <c r="G7" s="87"/>
+      <c r="H7" s="87"/>
     </row>
     <row r="8" spans="1:10" s="2" customFormat="1" ht="25.5" customHeight="1">
       <c r="C8" s="27" t="s">
         <v>44</v>
       </c>
       <c r="D8" s="24"/>
-      <c r="E8" s="87">
+      <c r="E8" s="88">
         <v>44316</v>
       </c>
-      <c r="F8" s="87"/>
-      <c r="G8" s="87"/>
-      <c r="H8" s="87"/>
+      <c r="F8" s="88"/>
+      <c r="G8" s="88"/>
+      <c r="H8" s="88"/>
     </row>
     <row r="9" spans="1:10" ht="24.75" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
-      <c r="C9" s="82" t="s">
+      <c r="C9" s="83" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="82"/>
-      <c r="E9" s="82"/>
-      <c r="F9" s="82"/>
-      <c r="G9" s="82"/>
-      <c r="H9" s="82"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="83"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
     </row>
@@ -3757,13 +3752,13 @@
       <c r="B11" s="32"/>
       <c r="C11" s="32"/>
       <c r="D11" s="2"/>
-      <c r="F11" s="84" t="s">
+      <c r="F11" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="G11" s="84"/>
-      <c r="H11" s="84"/>
-      <c r="I11" s="84"/>
-      <c r="J11" s="84"/>
+      <c r="G11" s="85"/>
+      <c r="H11" s="85"/>
+      <c r="I11" s="85"/>
+      <c r="J11" s="85"/>
     </row>
     <row r="12" spans="1:10" ht="20" customHeight="1">
       <c r="A12" s="31" t="s">
@@ -3772,20 +3767,20 @@
       <c r="B12" s="32"/>
       <c r="C12" s="32"/>
       <c r="D12" s="2"/>
-      <c r="F12" s="83" t="s">
+      <c r="F12" s="84" t="s">
         <v>40</v>
       </c>
-      <c r="G12" s="83"/>
-      <c r="H12" s="83"/>
-      <c r="I12" s="83"/>
-      <c r="J12" s="83"/>
+      <c r="G12" s="84"/>
+      <c r="H12" s="84"/>
+      <c r="I12" s="84"/>
+      <c r="J12" s="84"/>
     </row>
     <row r="13" spans="1:10" ht="20" customHeight="1">
       <c r="A13" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="78"/>
-      <c r="C13" s="78"/>
+      <c r="B13" s="79"/>
+      <c r="C13" s="79"/>
       <c r="D13" s="2"/>
       <c r="F13" s="5" t="s">
         <v>39</v>
@@ -3799,8 +3794,8 @@
       <c r="A14" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="78"/>
-      <c r="C14" s="78"/>
+      <c r="B14" s="79"/>
+      <c r="C14" s="79"/>
       <c r="D14" s="2"/>
       <c r="F14" s="5" t="s">
         <v>45</v>
@@ -3891,6 +3886,1046 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="TemplateFile" ma:contentTypeID="0x010100F6E1CA76AAD4564AAF106FC3CFA868360400186944AA932D8046A3B88E9B37BEBDF5" ma:contentTypeVersion="57" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="99516f8994b63f46a279aa564b61ee37">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1119c2e5-8fb9-4d5f-baf1-202c530f2c34" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4ccc0999b57010467b6aff3ba0e15941" ns2:_="">
+    <xsd:import namespace="1119c2e5-8fb9-4d5f-baf1-202c530f2c34"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:AcquiredFrom" minOccurs="0"/>
+                <xsd:element ref="ns2:UACurrentWords" minOccurs="0"/>
+                <xsd:element ref="ns2:TPApplication" minOccurs="0"/>
+                <xsd:element ref="ns2:ApprovalLog" minOccurs="0"/>
+                <xsd:element ref="ns2:ApprovalStatus" minOccurs="0"/>
+                <xsd:element ref="ns2:AssetStart" minOccurs="0"/>
+                <xsd:element ref="ns2:AssetExpire" minOccurs="0"/>
+                <xsd:element ref="ns2:AssetId" minOccurs="0"/>
+                <xsd:element ref="ns2:IsSearchable" minOccurs="0"/>
+                <xsd:element ref="ns2:AssetType" minOccurs="0"/>
+                <xsd:element ref="ns2:APAuthor" minOccurs="0"/>
+                <xsd:element ref="ns2:AverageRating" minOccurs="0"/>
+                <xsd:element ref="ns2:BlockPublish" minOccurs="0"/>
+                <xsd:element ref="ns2:BugNumber" minOccurs="0"/>
+                <xsd:element ref="ns2:CampaignTagsTaxHTField0" minOccurs="0"/>
+                <xsd:element ref="ns2:TPClientViewer" minOccurs="0"/>
+                <xsd:element ref="ns2:ClipArtFilename" minOccurs="0"/>
+                <xsd:element ref="ns2:TPCommandLine" minOccurs="0"/>
+                <xsd:element ref="ns2:TPComponent" minOccurs="0"/>
+                <xsd:element ref="ns2:ContentItem" minOccurs="0"/>
+                <xsd:element ref="ns2:CrawlForDependencies" minOccurs="0"/>
+                <xsd:element ref="ns2:CSXHash" minOccurs="0"/>
+                <xsd:element ref="ns2:CSXSubmissionMarket" minOccurs="0"/>
+                <xsd:element ref="ns2:CSXUpdate" minOccurs="0"/>
+                <xsd:element ref="ns2:IntlLangReviewDate" minOccurs="0"/>
+                <xsd:element ref="ns2:IsDeleted" minOccurs="0"/>
+                <xsd:element ref="ns2:APDescription" minOccurs="0"/>
+                <xsd:element ref="ns2:DirectSourceMarket" minOccurs="0"/>
+                <xsd:element ref="ns2:Downloads" minOccurs="0"/>
+                <xsd:element ref="ns2:DSATActionTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:APEditor" minOccurs="0"/>
+                <xsd:element ref="ns2:EditorialStatus" minOccurs="0"/>
+                <xsd:element ref="ns2:EditorialTags" minOccurs="0"/>
+                <xsd:element ref="ns2:TPExecutable" minOccurs="0"/>
+                <xsd:element ref="ns2:FeatureTagsTaxHTField0" minOccurs="0"/>
+                <xsd:element ref="ns2:TPFriendlyName" minOccurs="0"/>
+                <xsd:element ref="ns2:FriendlyTitle" minOccurs="0"/>
+                <xsd:element ref="ns2:PrimaryImageGen" minOccurs="0"/>
+                <xsd:element ref="ns2:HandoffToMSDN" minOccurs="0"/>
+                <xsd:element ref="ns2:InProjectListLookup" minOccurs="0"/>
+                <xsd:element ref="ns2:TPInstallLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:InternalTagsTaxHTField0" minOccurs="0"/>
+                <xsd:element ref="ns2:IntlLangReview" minOccurs="0"/>
+                <xsd:element ref="ns2:IntlLangReviewer" minOccurs="0"/>
+                <xsd:element ref="ns2:MarketSpecific" minOccurs="0"/>
+                <xsd:element ref="ns2:LastCompleteVersionLookup" minOccurs="0"/>
+                <xsd:element ref="ns2:LastHandOff" minOccurs="0"/>
+                <xsd:element ref="ns2:LastModifiedDateTime" minOccurs="0"/>
+                <xsd:element ref="ns2:LastPreviewErrorLookup" minOccurs="0"/>
+                <xsd:element ref="ns2:LastPreviewResultLookup" minOccurs="0"/>
+                <xsd:element ref="ns2:LastPreviewAttemptDateLookup" minOccurs="0"/>
+                <xsd:element ref="ns2:LastPreviewedByLookup" minOccurs="0"/>
+                <xsd:element ref="ns2:LastPreviewTimeLookup" minOccurs="0"/>
+                <xsd:element ref="ns2:LastPreviewVersionLookup" minOccurs="0"/>
+                <xsd:element ref="ns2:LastPublishErrorLookup" minOccurs="0"/>
+                <xsd:element ref="ns2:LastPublishResultLookup" minOccurs="0"/>
+                <xsd:element ref="ns2:LastPublishAttemptDateLookup" minOccurs="0"/>
+                <xsd:element ref="ns2:LastPublishedByLookup" minOccurs="0"/>
+                <xsd:element ref="ns2:LastPublishTimeLookup" minOccurs="0"/>
+                <xsd:element ref="ns2:LastPublishVersionLookup" minOccurs="0"/>
+                <xsd:element ref="ns2:TPLaunchHelpLinkType" minOccurs="0"/>
+                <xsd:element ref="ns2:LegacyData" minOccurs="0"/>
+                <xsd:element ref="ns2:TPLaunchHelpLink" minOccurs="0"/>
+                <xsd:element ref="ns2:LocComments" minOccurs="0"/>
+                <xsd:element ref="ns2:LocLastLocAttemptVersionLookup" minOccurs="0"/>
+                <xsd:element ref="ns2:LocLastLocAttemptVersionTypeLookup" minOccurs="0"/>
+                <xsd:element ref="ns2:LocManualTestRequired" minOccurs="0"/>
+                <xsd:element ref="ns2:LocMarketGroupTiers2" minOccurs="0"/>
+                <xsd:element ref="ns2:LocNewPublishedVersionLookup" minOccurs="0"/>
+                <xsd:element ref="ns2:LocOverallHandbackStatusLookup" minOccurs="0"/>
+                <xsd:element ref="ns2:LocOverallLocStatusLookup" minOccurs="0"/>
+                <xsd:element ref="ns2:LocOverallPreviewStatusLookup" minOccurs="0"/>
+                <xsd:element ref="ns2:LocOverallPublishStatusLookup" minOccurs="0"/>
+                <xsd:element ref="ns2:IntlLocPriority" minOccurs="0"/>
+                <xsd:element ref="ns2:LocProcessedForHandoffsLookup" minOccurs="0"/>
+                <xsd:element ref="ns2:LocProcessedForMarketsLookup" minOccurs="0"/>
+                <xsd:element ref="ns2:LocPublishedDependentAssetsLookup" minOccurs="0"/>
+                <xsd:element ref="ns2:LocPublishedLinkedAssetsLookup" minOccurs="0"/>
+                <xsd:element ref="ns2:LocRecommendedHandoff" minOccurs="0"/>
+                <xsd:element ref="ns2:LocalizationTagsTaxHTField0" minOccurs="0"/>
+                <xsd:element ref="ns2:MachineTranslated" minOccurs="0"/>
+                <xsd:element ref="ns2:Manager" minOccurs="0"/>
+                <xsd:element ref="ns2:Markets" minOccurs="0"/>
+                <xsd:element ref="ns2:Milestone" minOccurs="0"/>
+                <xsd:element ref="ns2:TPNamespace" minOccurs="0"/>
+                <xsd:element ref="ns2:NumericId" minOccurs="0"/>
+                <xsd:element ref="ns2:NumOfRatingsLookup" minOccurs="0"/>
+                <xsd:element ref="ns2:OOCacheId" minOccurs="0"/>
+                <xsd:element ref="ns2:OpenTemplate" minOccurs="0"/>
+                <xsd:element ref="ns2:OriginAsset" minOccurs="0"/>
+                <xsd:element ref="ns2:OriginalRelease" minOccurs="0"/>
+                <xsd:element ref="ns2:OriginalSourceMarket" minOccurs="0"/>
+                <xsd:element ref="ns2:OutputCachingOn" minOccurs="0"/>
+                <xsd:element ref="ns2:ParentAssetId" minOccurs="0"/>
+                <xsd:element ref="ns2:PlannedPubDate" minOccurs="0"/>
+                <xsd:element ref="ns2:PolicheckWords" minOccurs="0"/>
+                <xsd:element ref="ns2:BusinessGroup" minOccurs="0"/>
+                <xsd:element ref="ns2:UAProjectedTotalWords" minOccurs="0"/>
+                <xsd:element ref="ns2:Provider" minOccurs="0"/>
+                <xsd:element ref="ns2:Providers" minOccurs="0"/>
+                <xsd:element ref="ns2:PublishStatusLookup" minOccurs="0"/>
+                <xsd:element ref="ns2:PublishTargets" minOccurs="0"/>
+                <xsd:element ref="ns2:RecommendationsModifier" minOccurs="0"/>
+                <xsd:element ref="ns2:ArtSampleDocs" minOccurs="0"/>
+                <xsd:element ref="ns2:ScenarioTagsTaxHTField0" minOccurs="0"/>
+                <xsd:element ref="ns2:ShowIn" minOccurs="0"/>
+                <xsd:element ref="ns2:SourceTitle" minOccurs="0"/>
+                <xsd:element ref="ns2:CSXSubmissionDate" minOccurs="0"/>
+                <xsd:element ref="ns2:SubmitterId" minOccurs="0"/>
+                <xsd:element ref="ns2:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:TaxCatchAllLabel" minOccurs="0"/>
+                <xsd:element ref="ns2:TemplateStatus" minOccurs="0"/>
+                <xsd:element ref="ns2:TemplateTemplateType" minOccurs="0"/>
+                <xsd:element ref="ns2:ThumbnailAssetId" minOccurs="0"/>
+                <xsd:element ref="ns2:TimesCloned" minOccurs="0"/>
+                <xsd:element ref="ns2:TrustLevel" minOccurs="0"/>
+                <xsd:element ref="ns2:UALocComments" minOccurs="0"/>
+                <xsd:element ref="ns2:UALocRecommendation" minOccurs="0"/>
+                <xsd:element ref="ns2:UANotes" minOccurs="0"/>
+                <xsd:element ref="ns2:TPAppVersion" minOccurs="0"/>
+                <xsd:element ref="ns2:VoteCount" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="1119c2e5-8fb9-4d5f-baf1-202c530f2c34" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="AcquiredFrom" ma:index="1" nillable="true" ma:displayName="Acquired From" ma:default="Internal MS" ma:internalName="AcquiredFrom" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Choice">
+          <xsd:enumeration value="Internal MS"/>
+          <xsd:enumeration value="Community"/>
+          <xsd:enumeration value="MVP"/>
+          <xsd:enumeration value="Publisher"/>
+          <xsd:enumeration value="Partner"/>
+          <xsd:enumeration value="None"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="UACurrentWords" ma:index="2" nillable="true" ma:displayName="Actual Word Count" ma:default="" ma:internalName="UACurrentWords" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TPApplication" ma:index="3" nillable="true" ma:displayName="Application to Open Template With" ma:default="" ma:internalName="TPApplication">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="ApprovalLog" ma:index="4" nillable="true" ma:displayName="Approval Log" ma:default="" ma:hidden="true" ma:internalName="ApprovalLog" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="ApprovalStatus" ma:index="5" nillable="true" ma:displayName="Approval Status" ma:default="InProgress" ma:internalName="ApprovalStatus" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Choice">
+          <xsd:enumeration value="InProgress"/>
+          <xsd:enumeration value="Rejected"/>
+          <xsd:enumeration value="Questionable"/>
+          <xsd:enumeration value="ApprovedAutomatic"/>
+          <xsd:enumeration value="ApprovedManual"/>
+          <xsd:enumeration value="On Hold"/>
+          <xsd:enumeration value="Needs Review"/>
+          <xsd:enumeration value="A Violation"/>
+          <xsd:enumeration value="Unpublished Violation"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="AssetStart" ma:index="6" nillable="true" ma:displayName="Asset Begin Date" ma:default="[Today]" ma:internalName="AssetStart" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:DateTime"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="AssetExpire" ma:index="7" nillable="true" ma:displayName="Asset End Date" ma:default="2029-01-01T00:00:00Z" ma:internalName="AssetExpire" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:DateTime"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="AssetId" ma:index="8" nillable="true" ma:displayName="Asset ID" ma:default="" ma:indexed="true" ma:internalName="AssetId" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="IsSearchable" ma:index="9" nillable="true" ma:displayName="Asset Searchable?" ma:default="true" ma:internalName="IsSearchable" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Boolean"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="AssetType" ma:index="10" nillable="true" ma:displayName="Asset Type" ma:default="" ma:internalName="AssetType" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="APAuthor" ma:index="11" nillable="true" ma:displayName="Author" ma:default="" ma:list="UserInfo" ma:internalName="APAuthor" ma:readOnly="false">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:User">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="AverageRating" ma:index="12" nillable="true" ma:displayName="Average Rating" ma:internalName="AverageRating" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="BlockPublish" ma:index="13" nillable="true" ma:displayName="Block from Publishing?" ma:default="" ma:internalName="BlockPublish" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Boolean"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="BugNumber" ma:index="14" nillable="true" ma:displayName="Bug Number" ma:default="" ma:internalName="BugNumber" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="CampaignTagsTaxHTField0" ma:index="16" nillable="true" ma:taxonomy="true" ma:internalName="CampaignTagsTaxHTField0" ma:taxonomyFieldName="CampaignTags" ma:displayName="Campaigns" ma:readOnly="false" ma:default="" ma:fieldId="{04032b9e-8ee6-4e89-b9db-4ffff205d025}" ma:taxonomyMulti="true" ma:sspId="8f79753a-75d3-41f5-8ca3-40b843941b4f" ma:termSetId="ca0e50d4-faa1-44ce-961e-bb1441c60e66" ma:anchorId="00000000-0000-0000-0000-000000000000" ma:open="false" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="TPClientViewer" ma:index="17" nillable="true" ma:displayName="Client Viewer" ma:default="" ma:internalName="TPClientViewer">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="ClipArtFilename" ma:index="18" nillable="true" ma:displayName="Clip Art Name" ma:default="" ma:internalName="ClipArtFilename" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TPCommandLine" ma:index="19" nillable="true" ma:displayName="Command Line" ma:default="" ma:internalName="TPCommandLine">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TPComponent" ma:index="20" nillable="true" ma:displayName="Component" ma:default="" ma:internalName="TPComponent">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="ContentItem" ma:index="21" nillable="true" ma:displayName="Content Item" ma:default="" ma:hidden="true" ma:internalName="ContentItem" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="CrawlForDependencies" ma:index="23" nillable="true" ma:displayName="Crawl for Dependencies?" ma:default="true" ma:internalName="CrawlForDependencies" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Boolean"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="CSXHash" ma:index="26" nillable="true" ma:displayName="CSX Hash" ma:default="" ma:indexed="true" ma:internalName="CSXHash" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="CSXSubmissionMarket" ma:index="27" nillable="true" ma:displayName="CSX Submission Market" ma:default="" ma:list="{388FC2BA-F530-4FF7-911A-621CAE6AFBD3}" ma:internalName="CSXSubmissionMarket" ma:readOnly="false" ma:showField="MarketName" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Lookup"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="CSXUpdate" ma:index="28" nillable="true" ma:displayName="CSX Updated?" ma:default="false" ma:internalName="CSXUpdate" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Boolean"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="IntlLangReviewDate" ma:index="29" nillable="true" ma:displayName="Date to Complete Intl QA" ma:default="" ma:internalName="IntlLangReviewDate" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:DateTime"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="IsDeleted" ma:index="30" nillable="true" ma:displayName="Deleted?" ma:default="" ma:internalName="IsDeleted" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Boolean"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="APDescription" ma:index="31" nillable="true" ma:displayName="Description" ma:default="" ma:internalName="APDescription" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="DirectSourceMarket" ma:index="32" nillable="true" ma:displayName="Direct Source Market Group" ma:default="" ma:internalName="DirectSourceMarket" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="Downloads" ma:index="33" nillable="true" ma:displayName="Downloads" ma:default="0" ma:hidden="true" ma:internalName="Downloads" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="DSATActionTaken" ma:index="34" nillable="true" ma:displayName="DSAT Action Taken" ma:default="" ma:internalName="DSATActionTaken" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Choice">
+          <xsd:enumeration value="Best Bets"/>
+          <xsd:enumeration value="Expire"/>
+          <xsd:enumeration value="Hide"/>
+          <xsd:enumeration value="None"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="APEditor" ma:index="35" nillable="true" ma:displayName="Editor" ma:default="" ma:list="UserInfo" ma:internalName="APEditor" ma:readOnly="false">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:User">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="EditorialStatus" ma:index="36" nillable="true" ma:displayName="Editorial Status" ma:default="" ma:internalName="EditorialStatus" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="EditorialTags" ma:index="37" nillable="true" ma:displayName="Editorial Tags" ma:default="" ma:internalName="EditorialTags">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TPExecutable" ma:index="38" nillable="true" ma:displayName="Executable" ma:default="" ma:internalName="TPExecutable">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="FeatureTagsTaxHTField0" ma:index="40" nillable="true" ma:taxonomy="true" ma:internalName="FeatureTagsTaxHTField0" ma:taxonomyFieldName="FeatureTags" ma:displayName="Features" ma:readOnly="false" ma:default="" ma:fieldId="{5dcf7547-996b-4a0e-b7d1-0f761d14131b}" ma:taxonomyMulti="true" ma:sspId="8f79753a-75d3-41f5-8ca3-40b843941b4f" ma:termSetId="f1ab6845-967d-4854-a0ba-4ec07f0f8113" ma:anchorId="00000000-0000-0000-0000-000000000000" ma:open="false" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="TPFriendlyName" ma:index="41" nillable="true" ma:displayName="Friendly Name" ma:default="" ma:internalName="TPFriendlyName">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="FriendlyTitle" ma:index="42" nillable="true" ma:displayName="Friendly Title" ma:default="" ma:description="Shorter title to be used when displaying search results" ma:internalName="FriendlyTitle" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="PrimaryImageGen" ma:index="43" nillable="true" ma:displayName="Generate Images?" ma:default="true" ma:internalName="PrimaryImageGen">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Boolean"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="HandoffToMSDN" ma:index="44" nillable="true" ma:displayName="Handoff To MSDN Date" ma:default="" ma:internalName="HandoffToMSDN" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:DateTime"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="InProjectListLookup" ma:index="45" nillable="true" ma:displayName="InProjectListLookup" ma:list="{4D83B164-8C00-474C-8363-38E0B8FF22E3}" ma:internalName="InProjectListLookup" ma:readOnly="true" ma:showField="InProjectList" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="TPInstallLocation" ma:index="46" nillable="true" ma:displayName="Install Location" ma:default="" ma:internalName="TPInstallLocation">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="InternalTagsTaxHTField0" ma:index="48" nillable="true" ma:taxonomy="true" ma:internalName="InternalTagsTaxHTField0" ma:taxonomyFieldName="InternalTags" ma:displayName="Internal Tags" ma:readOnly="false" ma:default="" ma:fieldId="{e5aec8e1-0842-4156-acaa-2defcf90540a}" ma:taxonomyMulti="true" ma:sspId="8f79753a-75d3-41f5-8ca3-40b843941b4f" ma:termSetId="82b6639e-f7fc-4c18-ad2d-003a6e707765" ma:anchorId="00000000-0000-0000-0000-000000000000" ma:open="false" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="IntlLangReview" ma:index="49" nillable="true" ma:displayName="Intl Lang QA Review Required?" ma:default="" ma:internalName="IntlLangReview" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Boolean"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="IntlLangReviewer" ma:index="50" nillable="true" ma:displayName="Intl Lang QA Reviewer" ma:default="" ma:internalName="IntlLangReviewer" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MarketSpecific" ma:index="51" nillable="true" ma:displayName="Is Market Specific?" ma:default="" ma:internalName="MarketSpecific" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Boolean"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="LastCompleteVersionLookup" ma:index="52" nillable="true" ma:displayName="Last Complete Version Lookup" ma:default="" ma:list="{4D83B164-8C00-474C-8363-38E0B8FF22E3}" ma:internalName="LastCompleteVersionLookup" ma:readOnly="true" ma:showField="LastCompleteVersion" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="LastHandOff" ma:index="53" nillable="true" ma:displayName="Last Hand-off" ma:default="" ma:internalName="LastHandOff" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:DateTime"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="LastModifiedDateTime" ma:index="54" nillable="true" ma:displayName="Last Modified Date" ma:default="" ma:internalName="LastModifiedDateTime" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:DateTime"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="LastPreviewErrorLookup" ma:index="55" nillable="true" ma:displayName="Last Preview Attempt Error" ma:default="" ma:list="{4D83B164-8C00-474C-8363-38E0B8FF22E3}" ma:internalName="LastPreviewErrorLookup" ma:readOnly="true" ma:showField="LastPreviewError" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="LastPreviewResultLookup" ma:index="56" nillable="true" ma:displayName="Last Preview Attempt Result" ma:default="" ma:list="{4D83B164-8C00-474C-8363-38E0B8FF22E3}" ma:internalName="LastPreviewResultLookup" ma:readOnly="true" ma:showField="LastPreviewResult" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="LastPreviewAttemptDateLookup" ma:index="57" nillable="true" ma:displayName="Last Preview Attempted On" ma:default="" ma:list="{4D83B164-8C00-474C-8363-38E0B8FF22E3}" ma:internalName="LastPreviewAttemptDateLookup" ma:readOnly="true" ma:showField="LastPreviewAttemptDate" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="LastPreviewedByLookup" ma:index="58" nillable="true" ma:displayName="Last Previewed By" ma:default="" ma:list="{4D83B164-8C00-474C-8363-38E0B8FF22E3}" ma:internalName="LastPreviewedByLookup" ma:readOnly="true" ma:showField="LastPreviewedBy" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="LastPreviewTimeLookup" ma:index="59" nillable="true" ma:displayName="Last Previewed Date" ma:default="" ma:list="{4D83B164-8C00-474C-8363-38E0B8FF22E3}" ma:internalName="LastPreviewTimeLookup" ma:readOnly="true" ma:showField="LastPreviewTime" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="LastPreviewVersionLookup" ma:index="60" nillable="true" ma:displayName="Last Previewed Version" ma:default="" ma:list="{4D83B164-8C00-474C-8363-38E0B8FF22E3}" ma:internalName="LastPreviewVersionLookup" ma:readOnly="true" ma:showField="LastPreviewVersion" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="LastPublishErrorLookup" ma:index="61" nillable="true" ma:displayName="Last Publish Attempt Error" ma:default="" ma:list="{4D83B164-8C00-474C-8363-38E0B8FF22E3}" ma:internalName="LastPublishErrorLookup" ma:readOnly="true" ma:showField="LastPublishError" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="LastPublishResultLookup" ma:index="62" nillable="true" ma:displayName="Last Publish Attempt Result" ma:default="" ma:list="{4D83B164-8C00-474C-8363-38E0B8FF22E3}" ma:internalName="LastPublishResultLookup" ma:readOnly="true" ma:showField="LastPublishResult" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="LastPublishAttemptDateLookup" ma:index="63" nillable="true" ma:displayName="Last Publish Attempted On" ma:default="" ma:list="{4D83B164-8C00-474C-8363-38E0B8FF22E3}" ma:internalName="LastPublishAttemptDateLookup" ma:readOnly="true" ma:showField="LastPublishAttemptDate" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="LastPublishedByLookup" ma:index="64" nillable="true" ma:displayName="Last Published By" ma:default="" ma:list="{4D83B164-8C00-474C-8363-38E0B8FF22E3}" ma:internalName="LastPublishedByLookup" ma:readOnly="true" ma:showField="LastPublishedBy" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="LastPublishTimeLookup" ma:index="65" nillable="true" ma:displayName="Last Published Date" ma:default="" ma:list="{4D83B164-8C00-474C-8363-38E0B8FF22E3}" ma:internalName="LastPublishTimeLookup" ma:readOnly="true" ma:showField="LastPublishTime" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="LastPublishVersionLookup" ma:index="66" nillable="true" ma:displayName="Last Published Version" ma:default="" ma:list="{4D83B164-8C00-474C-8363-38E0B8FF22E3}" ma:internalName="LastPublishVersionLookup" ma:readOnly="true" ma:showField="LastPublishVersion" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="TPLaunchHelpLinkType" ma:index="67" nillable="true" ma:displayName="Launch Help Link Type" ma:default="Template" ma:internalName="TPLaunchHelpLinkType">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Choice">
+          <xsd:enumeration value="Template"/>
+          <xsd:enumeration value="Training"/>
+          <xsd:enumeration value="URL"/>
+          <xsd:enumeration value="None"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="LegacyData" ma:index="68" nillable="true" ma:displayName="Legacy Data" ma:default="" ma:internalName="LegacyData" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TPLaunchHelpLink" ma:index="69" nillable="true" ma:displayName="Link to Launch Help Topic" ma:default="" ma:internalName="TPLaunchHelpLink">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="LocComments" ma:index="70" nillable="true" ma:displayName="Loc Approval Comments" ma:default="" ma:internalName="LocComments" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="LocLastLocAttemptVersionLookup" ma:index="71" nillable="true" ma:displayName="Loc Last Loc Attempt Version" ma:default="" ma:list="{BC39992D-5589-4A4E-8B38-02E0637E5C25}" ma:internalName="LocLastLocAttemptVersionLookup" ma:readOnly="false" ma:showField="LastLocAttemptVersion" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Lookup"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="LocLastLocAttemptVersionTypeLookup" ma:index="72" nillable="true" ma:displayName="Loc Last Loc Attempt Version Type" ma:default="" ma:list="{BC39992D-5589-4A4E-8B38-02E0637E5C25}" ma:internalName="LocLastLocAttemptVersionTypeLookup" ma:readOnly="true" ma:showField="LastLocAttemptVersionType" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Lookup"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="LocManualTestRequired" ma:index="73" nillable="true" ma:displayName="Loc Manual Test Required" ma:default="" ma:internalName="LocManualTestRequired" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Boolean"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="LocMarketGroupTiers2" ma:index="74" nillable="true" ma:displayName="Loc Market Group Tiers" ma:internalName="LocMarketGroupTiers2" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="LocNewPublishedVersionLookup" ma:index="75" nillable="true" ma:displayName="Loc New Published Version Lookup" ma:default="" ma:list="{BC39992D-5589-4A4E-8B38-02E0637E5C25}" ma:internalName="LocNewPublishedVersionLookup" ma:readOnly="true" ma:showField="NewPublishedVersion" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Lookup"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="LocOverallHandbackStatusLookup" ma:index="76" nillable="true" ma:displayName="Loc Overall Handback Status" ma:default="" ma:list="{BC39992D-5589-4A4E-8B38-02E0637E5C25}" ma:internalName="LocOverallHandbackStatusLookup" ma:readOnly="true" ma:showField="OverallHandbackStatus" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Lookup"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="LocOverallLocStatusLookup" ma:index="77" nillable="true" ma:displayName="Loc Overall Localize Status" ma:default="" ma:list="{BC39992D-5589-4A4E-8B38-02E0637E5C25}" ma:internalName="LocOverallLocStatusLookup" ma:readOnly="true" ma:showField="OverallLocStatus" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Lookup"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="LocOverallPreviewStatusLookup" ma:index="78" nillable="true" ma:displayName="Loc Overall Preview Status" ma:default="" ma:list="{BC39992D-5589-4A4E-8B38-02E0637E5C25}" ma:internalName="LocOverallPreviewStatusLookup" ma:readOnly="true" ma:showField="OverallPreviewStatus" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Lookup"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="LocOverallPublishStatusLookup" ma:index="79" nillable="true" ma:displayName="Loc Overall Publish Status" ma:default="" ma:list="{BC39992D-5589-4A4E-8B38-02E0637E5C25}" ma:internalName="LocOverallPublishStatusLookup" ma:readOnly="true" ma:showField="OverallPublishStatus" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Lookup"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="IntlLocPriority" ma:index="80" nillable="true" ma:displayName="Loc Priority" ma:default="" ma:internalName="IntlLocPriority" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="LocProcessedForHandoffsLookup" ma:index="81" nillable="true" ma:displayName="Loc Processed For Handoffs" ma:default="" ma:list="{BC39992D-5589-4A4E-8B38-02E0637E5C25}" ma:internalName="LocProcessedForHandoffsLookup" ma:readOnly="true" ma:showField="ProcessedForHandoffs" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Lookup"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="LocProcessedForMarketsLookup" ma:index="82" nillable="true" ma:displayName="Loc Processed For Markets" ma:default="" ma:list="{BC39992D-5589-4A4E-8B38-02E0637E5C25}" ma:internalName="LocProcessedForMarketsLookup" ma:readOnly="true" ma:showField="ProcessedForMarkets" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Lookup"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="LocPublishedDependentAssetsLookup" ma:index="83" nillable="true" ma:displayName="Loc Published Dependent Assets" ma:default="" ma:list="{BC39992D-5589-4A4E-8B38-02E0637E5C25}" ma:internalName="LocPublishedDependentAssetsLookup" ma:readOnly="true" ma:showField="PublishedDependentAssets" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Lookup"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="LocPublishedLinkedAssetsLookup" ma:index="84" nillable="true" ma:displayName="Loc Published Linked Assets" ma:default="" ma:list="{BC39992D-5589-4A4E-8B38-02E0637E5C25}" ma:internalName="LocPublishedLinkedAssetsLookup" ma:readOnly="true" ma:showField="PublishedLinkedAssets" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Lookup"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="LocRecommendedHandoff" ma:index="85" nillable="true" ma:displayName="Loc Recommended Handoff" ma:default="" ma:indexed="true" ma:internalName="LocRecommendedHandoff" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="LocalizationTagsTaxHTField0" ma:index="87" nillable="true" ma:taxonomy="true" ma:internalName="LocalizationTagsTaxHTField0" ma:taxonomyFieldName="LocalizationTags" ma:displayName="Localization Tags" ma:readOnly="false" ma:default="" ma:fieldId="{28ca5b26-415b-4822-b35b-d9a845b1b83b}" ma:taxonomyMulti="true" ma:sspId="8f79753a-75d3-41f5-8ca3-40b843941b4f" ma:termSetId="5b7703a5-8e8b-4b58-8b31-1cea35331da3" ma:anchorId="00000000-0000-0000-0000-000000000000" ma:open="false" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MachineTranslated" ma:index="88" nillable="true" ma:displayName="Machine Translated" ma:default="" ma:internalName="MachineTranslated" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Boolean"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="Manager" ma:index="89" nillable="true" ma:displayName="Manager" ma:hidden="true" ma:internalName="Manager" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="Markets" ma:index="90" nillable="true" ma:displayName="Markets" ma:default="" ma:description="Leave blank to show in all markets" ma:list="{388FC2BA-F530-4FF7-911A-621CAE6AFBD3}" ma:internalName="Markets" ma:readOnly="false" ma:showField="MarketName" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="Milestone" ma:index="91" nillable="true" ma:displayName="Milestone" ma:default="" ma:internalName="Milestone" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TPNamespace" ma:index="94" nillable="true" ma:displayName="Namespace" ma:default="" ma:internalName="TPNamespace">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="NumericId" ma:index="95" nillable="true" ma:displayName="Numeric ID" ma:default="" ma:indexed="true" ma:internalName="NumericId" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Number"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="NumOfRatingsLookup" ma:index="96" nillable="true" ma:displayName="NumOfRatings" ma:default="" ma:list="{4D83B164-8C00-474C-8363-38E0B8FF22E3}" ma:internalName="NumOfRatingsLookup" ma:readOnly="true" ma:showField="NumOfRatings" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="OOCacheId" ma:index="97" nillable="true" ma:displayName="OOCacheId" ma:internalName="OOCacheId" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="OpenTemplate" ma:index="98" nillable="true" ma:displayName="Open Template" ma:default="true" ma:internalName="OpenTemplate">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Boolean"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="OriginAsset" ma:index="99" nillable="true" ma:displayName="Origin Asset" ma:default="" ma:internalName="OriginAsset" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="OriginalRelease" ma:index="100" nillable="true" ma:displayName="Original Release" ma:default="15" ma:internalName="OriginalRelease" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Choice">
+          <xsd:enumeration value="14"/>
+          <xsd:enumeration value="15"/>
+          <xsd:enumeration value="16"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="OriginalSourceMarket" ma:index="101" nillable="true" ma:displayName="Original Source Market Group" ma:default="" ma:internalName="OriginalSourceMarket" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="OutputCachingOn" ma:index="102" nillable="true" ma:displayName="Output Caching" ma:default="true" ma:hidden="true" ma:internalName="OutputCachingOn" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Boolean"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="ParentAssetId" ma:index="103" nillable="true" ma:displayName="Parent Asset Id" ma:default="" ma:internalName="ParentAssetId" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="PlannedPubDate" ma:index="104" nillable="true" ma:displayName="Planned Publish Date" ma:default="" ma:indexed="true" ma:internalName="PlannedPubDate" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:DateTime"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="PolicheckWords" ma:index="105" nillable="true" ma:displayName="Policheck Words" ma:default="" ma:internalName="PolicheckWords" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="BusinessGroup" ma:index="106" nillable="true" ma:displayName="Product Division Owner" ma:default="" ma:internalName="BusinessGroup" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="UAProjectedTotalWords" ma:index="107" nillable="true" ma:displayName="Projected Word Count" ma:default="" ma:internalName="UAProjectedTotalWords" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="Provider" ma:index="108" nillable="true" ma:displayName="Provider" ma:default="" ma:internalName="Provider" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="Providers" ma:index="109" nillable="true" ma:displayName="Providers" ma:default="" ma:internalName="Providers">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="PublishStatusLookup" ma:index="110" nillable="true" ma:displayName="Publish Status" ma:default="" ma:list="{4D83B164-8C00-474C-8363-38E0B8FF22E3}" ma:internalName="PublishStatusLookup" ma:readOnly="false" ma:showField="PublishStatus" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="PublishTargets" ma:index="111" nillable="true" ma:displayName="Publish Target" ma:default="OfficeOnlineVNext" ma:internalName="PublishTargets" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="RecommendationsModifier" ma:index="112" nillable="true" ma:displayName="Recommendations Modifier" ma:default="" ma:internalName="RecommendationsModifier" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Number"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="ArtSampleDocs" ma:index="113" nillable="true" ma:displayName="Sample Docs" ma:default="" ma:hidden="true" ma:internalName="ArtSampleDocs" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="ScenarioTagsTaxHTField0" ma:index="115" nillable="true" ma:taxonomy="true" ma:internalName="ScenarioTagsTaxHTField0" ma:taxonomyFieldName="ScenarioTags" ma:displayName="Scenarios" ma:readOnly="false" ma:default="" ma:fieldId="{1c8e7b99-44ca-46c8-84b8-12cd8d7cf8ee}" ma:taxonomyMulti="true" ma:sspId="8f79753a-75d3-41f5-8ca3-40b843941b4f" ma:termSetId="4b7d5f16-e2f2-4fc0-bab3-6e8b931e57d6" ma:anchorId="00000000-0000-0000-0000-000000000000" ma:open="false" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="ShowIn" ma:index="117" nillable="true" ma:displayName="Show In" ma:default="Show everywhere" ma:internalName="ShowIn" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Choice">
+          <xsd:enumeration value="Hide on web"/>
+          <xsd:enumeration value="On Web no search"/>
+          <xsd:enumeration value="Show everywhere"/>
+          <xsd:enumeration value="Special use only"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="SourceTitle" ma:index="118" nillable="true" ma:displayName="Source Title" ma:default="" ma:indexed="true" ma:internalName="SourceTitle" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="CSXSubmissionDate" ma:index="119" nillable="true" ma:displayName="Submission Date" ma:default="" ma:internalName="CSXSubmissionDate" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:DateTime"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="SubmitterId" ma:index="120" nillable="true" ma:displayName="Submitter ID" ma:default="" ma:internalName="SubmitterId" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="121" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c59171da-55f1-4c8b-8421-0d1d3f99d741}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAllLabel" ma:index="122" nillable="true" ma:displayName="Taxonomy Catch All Column1" ma:hidden="true" ma:list="{c59171da-55f1-4c8b-8421-0d1d3f99d741}" ma:internalName="TaxCatchAllLabel" ma:readOnly="true" ma:showField="CatchAllDataLabel" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="TemplateStatus" ma:index="123" nillable="true" ma:displayName="Template Status" ma:default="" ma:internalName="TemplateStatus">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TemplateTemplateType" ma:index="124" nillable="true" ma:displayName="Template Type" ma:default="" ma:internalName="TemplateTemplateType">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="ThumbnailAssetId" ma:index="125" nillable="true" ma:displayName="Thumbnail Image Asset" ma:default="" ma:internalName="ThumbnailAssetId" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TimesCloned" ma:index="126" nillable="true" ma:displayName="Times Cloned" ma:default="" ma:internalName="TimesCloned" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Number"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TrustLevel" ma:index="128" nillable="true" ma:displayName="Trust Level" ma:default="1 Microsoft Managed Content" ma:internalName="TrustLevel" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="UALocComments" ma:index="129" nillable="true" ma:displayName="UA Loc Comments" ma:default="" ma:internalName="UALocComments" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="UALocRecommendation" ma:index="130" nillable="true" ma:displayName="UA Loc Recommendation" ma:default="Localize" ma:internalName="UALocRecommendation" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Choice">
+          <xsd:enumeration value="Localize"/>
+          <xsd:enumeration value="Never Localize"/>
+          <xsd:enumeration value="Priority Localize"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="UANotes" ma:index="131" nillable="true" ma:displayName="UA Notes" ma:default="" ma:internalName="UANotes" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TPAppVersion" ma:index="132" nillable="true" ma:displayName="Version" ma:default="" ma:internalName="TPAppVersion">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="VoteCount" ma:index="133" nillable="true" ma:displayName="Vote Count" ma:default="" ma:internalName="VoteCount" ma:readOnly="false">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="22" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="127" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <DirectSourceMarket xmlns="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">english</DirectSourceMarket>
@@ -4028,1046 +5063,6 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="TemplateFile" ma:contentTypeID="0x010100F6E1CA76AAD4564AAF106FC3CFA868360400186944AA932D8046A3B88E9B37BEBDF5" ma:contentTypeVersion="57" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="99516f8994b63f46a279aa564b61ee37">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1119c2e5-8fb9-4d5f-baf1-202c530f2c34" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4ccc0999b57010467b6aff3ba0e15941" ns2:_="">
-    <xsd:import namespace="1119c2e5-8fb9-4d5f-baf1-202c530f2c34"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:AcquiredFrom" minOccurs="0"/>
-                <xsd:element ref="ns2:UACurrentWords" minOccurs="0"/>
-                <xsd:element ref="ns2:TPApplication" minOccurs="0"/>
-                <xsd:element ref="ns2:ApprovalLog" minOccurs="0"/>
-                <xsd:element ref="ns2:ApprovalStatus" minOccurs="0"/>
-                <xsd:element ref="ns2:AssetStart" minOccurs="0"/>
-                <xsd:element ref="ns2:AssetExpire" minOccurs="0"/>
-                <xsd:element ref="ns2:AssetId" minOccurs="0"/>
-                <xsd:element ref="ns2:IsSearchable" minOccurs="0"/>
-                <xsd:element ref="ns2:AssetType" minOccurs="0"/>
-                <xsd:element ref="ns2:APAuthor" minOccurs="0"/>
-                <xsd:element ref="ns2:AverageRating" minOccurs="0"/>
-                <xsd:element ref="ns2:BlockPublish" minOccurs="0"/>
-                <xsd:element ref="ns2:BugNumber" minOccurs="0"/>
-                <xsd:element ref="ns2:CampaignTagsTaxHTField0" minOccurs="0"/>
-                <xsd:element ref="ns2:TPClientViewer" minOccurs="0"/>
-                <xsd:element ref="ns2:ClipArtFilename" minOccurs="0"/>
-                <xsd:element ref="ns2:TPCommandLine" minOccurs="0"/>
-                <xsd:element ref="ns2:TPComponent" minOccurs="0"/>
-                <xsd:element ref="ns2:ContentItem" minOccurs="0"/>
-                <xsd:element ref="ns2:CrawlForDependencies" minOccurs="0"/>
-                <xsd:element ref="ns2:CSXHash" minOccurs="0"/>
-                <xsd:element ref="ns2:CSXSubmissionMarket" minOccurs="0"/>
-                <xsd:element ref="ns2:CSXUpdate" minOccurs="0"/>
-                <xsd:element ref="ns2:IntlLangReviewDate" minOccurs="0"/>
-                <xsd:element ref="ns2:IsDeleted" minOccurs="0"/>
-                <xsd:element ref="ns2:APDescription" minOccurs="0"/>
-                <xsd:element ref="ns2:DirectSourceMarket" minOccurs="0"/>
-                <xsd:element ref="ns2:Downloads" minOccurs="0"/>
-                <xsd:element ref="ns2:DSATActionTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:APEditor" minOccurs="0"/>
-                <xsd:element ref="ns2:EditorialStatus" minOccurs="0"/>
-                <xsd:element ref="ns2:EditorialTags" minOccurs="0"/>
-                <xsd:element ref="ns2:TPExecutable" minOccurs="0"/>
-                <xsd:element ref="ns2:FeatureTagsTaxHTField0" minOccurs="0"/>
-                <xsd:element ref="ns2:TPFriendlyName" minOccurs="0"/>
-                <xsd:element ref="ns2:FriendlyTitle" minOccurs="0"/>
-                <xsd:element ref="ns2:PrimaryImageGen" minOccurs="0"/>
-                <xsd:element ref="ns2:HandoffToMSDN" minOccurs="0"/>
-                <xsd:element ref="ns2:InProjectListLookup" minOccurs="0"/>
-                <xsd:element ref="ns2:TPInstallLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:InternalTagsTaxHTField0" minOccurs="0"/>
-                <xsd:element ref="ns2:IntlLangReview" minOccurs="0"/>
-                <xsd:element ref="ns2:IntlLangReviewer" minOccurs="0"/>
-                <xsd:element ref="ns2:MarketSpecific" minOccurs="0"/>
-                <xsd:element ref="ns2:LastCompleteVersionLookup" minOccurs="0"/>
-                <xsd:element ref="ns2:LastHandOff" minOccurs="0"/>
-                <xsd:element ref="ns2:LastModifiedDateTime" minOccurs="0"/>
-                <xsd:element ref="ns2:LastPreviewErrorLookup" minOccurs="0"/>
-                <xsd:element ref="ns2:LastPreviewResultLookup" minOccurs="0"/>
-                <xsd:element ref="ns2:LastPreviewAttemptDateLookup" minOccurs="0"/>
-                <xsd:element ref="ns2:LastPreviewedByLookup" minOccurs="0"/>
-                <xsd:element ref="ns2:LastPreviewTimeLookup" minOccurs="0"/>
-                <xsd:element ref="ns2:LastPreviewVersionLookup" minOccurs="0"/>
-                <xsd:element ref="ns2:LastPublishErrorLookup" minOccurs="0"/>
-                <xsd:element ref="ns2:LastPublishResultLookup" minOccurs="0"/>
-                <xsd:element ref="ns2:LastPublishAttemptDateLookup" minOccurs="0"/>
-                <xsd:element ref="ns2:LastPublishedByLookup" minOccurs="0"/>
-                <xsd:element ref="ns2:LastPublishTimeLookup" minOccurs="0"/>
-                <xsd:element ref="ns2:LastPublishVersionLookup" minOccurs="0"/>
-                <xsd:element ref="ns2:TPLaunchHelpLinkType" minOccurs="0"/>
-                <xsd:element ref="ns2:LegacyData" minOccurs="0"/>
-                <xsd:element ref="ns2:TPLaunchHelpLink" minOccurs="0"/>
-                <xsd:element ref="ns2:LocComments" minOccurs="0"/>
-                <xsd:element ref="ns2:LocLastLocAttemptVersionLookup" minOccurs="0"/>
-                <xsd:element ref="ns2:LocLastLocAttemptVersionTypeLookup" minOccurs="0"/>
-                <xsd:element ref="ns2:LocManualTestRequired" minOccurs="0"/>
-                <xsd:element ref="ns2:LocMarketGroupTiers2" minOccurs="0"/>
-                <xsd:element ref="ns2:LocNewPublishedVersionLookup" minOccurs="0"/>
-                <xsd:element ref="ns2:LocOverallHandbackStatusLookup" minOccurs="0"/>
-                <xsd:element ref="ns2:LocOverallLocStatusLookup" minOccurs="0"/>
-                <xsd:element ref="ns2:LocOverallPreviewStatusLookup" minOccurs="0"/>
-                <xsd:element ref="ns2:LocOverallPublishStatusLookup" minOccurs="0"/>
-                <xsd:element ref="ns2:IntlLocPriority" minOccurs="0"/>
-                <xsd:element ref="ns2:LocProcessedForHandoffsLookup" minOccurs="0"/>
-                <xsd:element ref="ns2:LocProcessedForMarketsLookup" minOccurs="0"/>
-                <xsd:element ref="ns2:LocPublishedDependentAssetsLookup" minOccurs="0"/>
-                <xsd:element ref="ns2:LocPublishedLinkedAssetsLookup" minOccurs="0"/>
-                <xsd:element ref="ns2:LocRecommendedHandoff" minOccurs="0"/>
-                <xsd:element ref="ns2:LocalizationTagsTaxHTField0" minOccurs="0"/>
-                <xsd:element ref="ns2:MachineTranslated" minOccurs="0"/>
-                <xsd:element ref="ns2:Manager" minOccurs="0"/>
-                <xsd:element ref="ns2:Markets" minOccurs="0"/>
-                <xsd:element ref="ns2:Milestone" minOccurs="0"/>
-                <xsd:element ref="ns2:TPNamespace" minOccurs="0"/>
-                <xsd:element ref="ns2:NumericId" minOccurs="0"/>
-                <xsd:element ref="ns2:NumOfRatingsLookup" minOccurs="0"/>
-                <xsd:element ref="ns2:OOCacheId" minOccurs="0"/>
-                <xsd:element ref="ns2:OpenTemplate" minOccurs="0"/>
-                <xsd:element ref="ns2:OriginAsset" minOccurs="0"/>
-                <xsd:element ref="ns2:OriginalRelease" minOccurs="0"/>
-                <xsd:element ref="ns2:OriginalSourceMarket" minOccurs="0"/>
-                <xsd:element ref="ns2:OutputCachingOn" minOccurs="0"/>
-                <xsd:element ref="ns2:ParentAssetId" minOccurs="0"/>
-                <xsd:element ref="ns2:PlannedPubDate" minOccurs="0"/>
-                <xsd:element ref="ns2:PolicheckWords" minOccurs="0"/>
-                <xsd:element ref="ns2:BusinessGroup" minOccurs="0"/>
-                <xsd:element ref="ns2:UAProjectedTotalWords" minOccurs="0"/>
-                <xsd:element ref="ns2:Provider" minOccurs="0"/>
-                <xsd:element ref="ns2:Providers" minOccurs="0"/>
-                <xsd:element ref="ns2:PublishStatusLookup" minOccurs="0"/>
-                <xsd:element ref="ns2:PublishTargets" minOccurs="0"/>
-                <xsd:element ref="ns2:RecommendationsModifier" minOccurs="0"/>
-                <xsd:element ref="ns2:ArtSampleDocs" minOccurs="0"/>
-                <xsd:element ref="ns2:ScenarioTagsTaxHTField0" minOccurs="0"/>
-                <xsd:element ref="ns2:ShowIn" minOccurs="0"/>
-                <xsd:element ref="ns2:SourceTitle" minOccurs="0"/>
-                <xsd:element ref="ns2:CSXSubmissionDate" minOccurs="0"/>
-                <xsd:element ref="ns2:SubmitterId" minOccurs="0"/>
-                <xsd:element ref="ns2:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:TaxCatchAllLabel" minOccurs="0"/>
-                <xsd:element ref="ns2:TemplateStatus" minOccurs="0"/>
-                <xsd:element ref="ns2:TemplateTemplateType" minOccurs="0"/>
-                <xsd:element ref="ns2:ThumbnailAssetId" minOccurs="0"/>
-                <xsd:element ref="ns2:TimesCloned" minOccurs="0"/>
-                <xsd:element ref="ns2:TrustLevel" minOccurs="0"/>
-                <xsd:element ref="ns2:UALocComments" minOccurs="0"/>
-                <xsd:element ref="ns2:UALocRecommendation" minOccurs="0"/>
-                <xsd:element ref="ns2:UANotes" minOccurs="0"/>
-                <xsd:element ref="ns2:TPAppVersion" minOccurs="0"/>
-                <xsd:element ref="ns2:VoteCount" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="1119c2e5-8fb9-4d5f-baf1-202c530f2c34" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="AcquiredFrom" ma:index="1" nillable="true" ma:displayName="Acquired From" ma:default="Internal MS" ma:internalName="AcquiredFrom" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Choice">
-          <xsd:enumeration value="Internal MS"/>
-          <xsd:enumeration value="Community"/>
-          <xsd:enumeration value="MVP"/>
-          <xsd:enumeration value="Publisher"/>
-          <xsd:enumeration value="Partner"/>
-          <xsd:enumeration value="None"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="UACurrentWords" ma:index="2" nillable="true" ma:displayName="Actual Word Count" ma:default="" ma:internalName="UACurrentWords" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TPApplication" ma:index="3" nillable="true" ma:displayName="Application to Open Template With" ma:default="" ma:internalName="TPApplication">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="ApprovalLog" ma:index="4" nillable="true" ma:displayName="Approval Log" ma:default="" ma:hidden="true" ma:internalName="ApprovalLog" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="ApprovalStatus" ma:index="5" nillable="true" ma:displayName="Approval Status" ma:default="InProgress" ma:internalName="ApprovalStatus" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Choice">
-          <xsd:enumeration value="InProgress"/>
-          <xsd:enumeration value="Rejected"/>
-          <xsd:enumeration value="Questionable"/>
-          <xsd:enumeration value="ApprovedAutomatic"/>
-          <xsd:enumeration value="ApprovedManual"/>
-          <xsd:enumeration value="On Hold"/>
-          <xsd:enumeration value="Needs Review"/>
-          <xsd:enumeration value="A Violation"/>
-          <xsd:enumeration value="Unpublished Violation"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="AssetStart" ma:index="6" nillable="true" ma:displayName="Asset Begin Date" ma:default="[Today]" ma:internalName="AssetStart" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:DateTime"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="AssetExpire" ma:index="7" nillable="true" ma:displayName="Asset End Date" ma:default="2029-01-01T00:00:00Z" ma:internalName="AssetExpire" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:DateTime"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="AssetId" ma:index="8" nillable="true" ma:displayName="Asset ID" ma:default="" ma:indexed="true" ma:internalName="AssetId" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="IsSearchable" ma:index="9" nillable="true" ma:displayName="Asset Searchable?" ma:default="true" ma:internalName="IsSearchable" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Boolean"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="AssetType" ma:index="10" nillable="true" ma:displayName="Asset Type" ma:default="" ma:internalName="AssetType" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="APAuthor" ma:index="11" nillable="true" ma:displayName="Author" ma:default="" ma:list="UserInfo" ma:internalName="APAuthor" ma:readOnly="false">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:User">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="AverageRating" ma:index="12" nillable="true" ma:displayName="Average Rating" ma:internalName="AverageRating" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="BlockPublish" ma:index="13" nillable="true" ma:displayName="Block from Publishing?" ma:default="" ma:internalName="BlockPublish" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Boolean"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="BugNumber" ma:index="14" nillable="true" ma:displayName="Bug Number" ma:default="" ma:internalName="BugNumber" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="CampaignTagsTaxHTField0" ma:index="16" nillable="true" ma:taxonomy="true" ma:internalName="CampaignTagsTaxHTField0" ma:taxonomyFieldName="CampaignTags" ma:displayName="Campaigns" ma:readOnly="false" ma:default="" ma:fieldId="{04032b9e-8ee6-4e89-b9db-4ffff205d025}" ma:taxonomyMulti="true" ma:sspId="8f79753a-75d3-41f5-8ca3-40b843941b4f" ma:termSetId="ca0e50d4-faa1-44ce-961e-bb1441c60e66" ma:anchorId="00000000-0000-0000-0000-000000000000" ma:open="false" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="TPClientViewer" ma:index="17" nillable="true" ma:displayName="Client Viewer" ma:default="" ma:internalName="TPClientViewer">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="ClipArtFilename" ma:index="18" nillable="true" ma:displayName="Clip Art Name" ma:default="" ma:internalName="ClipArtFilename" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TPCommandLine" ma:index="19" nillable="true" ma:displayName="Command Line" ma:default="" ma:internalName="TPCommandLine">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TPComponent" ma:index="20" nillable="true" ma:displayName="Component" ma:default="" ma:internalName="TPComponent">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="ContentItem" ma:index="21" nillable="true" ma:displayName="Content Item" ma:default="" ma:hidden="true" ma:internalName="ContentItem" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="CrawlForDependencies" ma:index="23" nillable="true" ma:displayName="Crawl for Dependencies?" ma:default="true" ma:internalName="CrawlForDependencies" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Boolean"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="CSXHash" ma:index="26" nillable="true" ma:displayName="CSX Hash" ma:default="" ma:indexed="true" ma:internalName="CSXHash" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="CSXSubmissionMarket" ma:index="27" nillable="true" ma:displayName="CSX Submission Market" ma:default="" ma:list="{388FC2BA-F530-4FF7-911A-621CAE6AFBD3}" ma:internalName="CSXSubmissionMarket" ma:readOnly="false" ma:showField="MarketName" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Lookup"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="CSXUpdate" ma:index="28" nillable="true" ma:displayName="CSX Updated?" ma:default="false" ma:internalName="CSXUpdate" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Boolean"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="IntlLangReviewDate" ma:index="29" nillable="true" ma:displayName="Date to Complete Intl QA" ma:default="" ma:internalName="IntlLangReviewDate" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:DateTime"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="IsDeleted" ma:index="30" nillable="true" ma:displayName="Deleted?" ma:default="" ma:internalName="IsDeleted" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Boolean"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="APDescription" ma:index="31" nillable="true" ma:displayName="Description" ma:default="" ma:internalName="APDescription" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="DirectSourceMarket" ma:index="32" nillable="true" ma:displayName="Direct Source Market Group" ma:default="" ma:internalName="DirectSourceMarket" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Downloads" ma:index="33" nillable="true" ma:displayName="Downloads" ma:default="0" ma:hidden="true" ma:internalName="Downloads" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="DSATActionTaken" ma:index="34" nillable="true" ma:displayName="DSAT Action Taken" ma:default="" ma:internalName="DSATActionTaken" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Choice">
-          <xsd:enumeration value="Best Bets"/>
-          <xsd:enumeration value="Expire"/>
-          <xsd:enumeration value="Hide"/>
-          <xsd:enumeration value="None"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="APEditor" ma:index="35" nillable="true" ma:displayName="Editor" ma:default="" ma:list="UserInfo" ma:internalName="APEditor" ma:readOnly="false">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:User">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="EditorialStatus" ma:index="36" nillable="true" ma:displayName="Editorial Status" ma:default="" ma:internalName="EditorialStatus" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="EditorialTags" ma:index="37" nillable="true" ma:displayName="Editorial Tags" ma:default="" ma:internalName="EditorialTags">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TPExecutable" ma:index="38" nillable="true" ma:displayName="Executable" ma:default="" ma:internalName="TPExecutable">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="FeatureTagsTaxHTField0" ma:index="40" nillable="true" ma:taxonomy="true" ma:internalName="FeatureTagsTaxHTField0" ma:taxonomyFieldName="FeatureTags" ma:displayName="Features" ma:readOnly="false" ma:default="" ma:fieldId="{5dcf7547-996b-4a0e-b7d1-0f761d14131b}" ma:taxonomyMulti="true" ma:sspId="8f79753a-75d3-41f5-8ca3-40b843941b4f" ma:termSetId="f1ab6845-967d-4854-a0ba-4ec07f0f8113" ma:anchorId="00000000-0000-0000-0000-000000000000" ma:open="false" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="TPFriendlyName" ma:index="41" nillable="true" ma:displayName="Friendly Name" ma:default="" ma:internalName="TPFriendlyName">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="FriendlyTitle" ma:index="42" nillable="true" ma:displayName="Friendly Title" ma:default="" ma:description="Shorter title to be used when displaying search results" ma:internalName="FriendlyTitle" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="PrimaryImageGen" ma:index="43" nillable="true" ma:displayName="Generate Images?" ma:default="true" ma:internalName="PrimaryImageGen">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Boolean"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="HandoffToMSDN" ma:index="44" nillable="true" ma:displayName="Handoff To MSDN Date" ma:default="" ma:internalName="HandoffToMSDN" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:DateTime"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="InProjectListLookup" ma:index="45" nillable="true" ma:displayName="InProjectListLookup" ma:list="{4D83B164-8C00-474C-8363-38E0B8FF22E3}" ma:internalName="InProjectListLookup" ma:readOnly="true" ma:showField="InProjectList" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="TPInstallLocation" ma:index="46" nillable="true" ma:displayName="Install Location" ma:default="" ma:internalName="TPInstallLocation">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="InternalTagsTaxHTField0" ma:index="48" nillable="true" ma:taxonomy="true" ma:internalName="InternalTagsTaxHTField0" ma:taxonomyFieldName="InternalTags" ma:displayName="Internal Tags" ma:readOnly="false" ma:default="" ma:fieldId="{e5aec8e1-0842-4156-acaa-2defcf90540a}" ma:taxonomyMulti="true" ma:sspId="8f79753a-75d3-41f5-8ca3-40b843941b4f" ma:termSetId="82b6639e-f7fc-4c18-ad2d-003a6e707765" ma:anchorId="00000000-0000-0000-0000-000000000000" ma:open="false" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="IntlLangReview" ma:index="49" nillable="true" ma:displayName="Intl Lang QA Review Required?" ma:default="" ma:internalName="IntlLangReview" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Boolean"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="IntlLangReviewer" ma:index="50" nillable="true" ma:displayName="Intl Lang QA Reviewer" ma:default="" ma:internalName="IntlLangReviewer" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MarketSpecific" ma:index="51" nillable="true" ma:displayName="Is Market Specific?" ma:default="" ma:internalName="MarketSpecific" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Boolean"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="LastCompleteVersionLookup" ma:index="52" nillable="true" ma:displayName="Last Complete Version Lookup" ma:default="" ma:list="{4D83B164-8C00-474C-8363-38E0B8FF22E3}" ma:internalName="LastCompleteVersionLookup" ma:readOnly="true" ma:showField="LastCompleteVersion" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="LastHandOff" ma:index="53" nillable="true" ma:displayName="Last Hand-off" ma:default="" ma:internalName="LastHandOff" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:DateTime"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="LastModifiedDateTime" ma:index="54" nillable="true" ma:displayName="Last Modified Date" ma:default="" ma:internalName="LastModifiedDateTime" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:DateTime"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="LastPreviewErrorLookup" ma:index="55" nillable="true" ma:displayName="Last Preview Attempt Error" ma:default="" ma:list="{4D83B164-8C00-474C-8363-38E0B8FF22E3}" ma:internalName="LastPreviewErrorLookup" ma:readOnly="true" ma:showField="LastPreviewError" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="LastPreviewResultLookup" ma:index="56" nillable="true" ma:displayName="Last Preview Attempt Result" ma:default="" ma:list="{4D83B164-8C00-474C-8363-38E0B8FF22E3}" ma:internalName="LastPreviewResultLookup" ma:readOnly="true" ma:showField="LastPreviewResult" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="LastPreviewAttemptDateLookup" ma:index="57" nillable="true" ma:displayName="Last Preview Attempted On" ma:default="" ma:list="{4D83B164-8C00-474C-8363-38E0B8FF22E3}" ma:internalName="LastPreviewAttemptDateLookup" ma:readOnly="true" ma:showField="LastPreviewAttemptDate" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="LastPreviewedByLookup" ma:index="58" nillable="true" ma:displayName="Last Previewed By" ma:default="" ma:list="{4D83B164-8C00-474C-8363-38E0B8FF22E3}" ma:internalName="LastPreviewedByLookup" ma:readOnly="true" ma:showField="LastPreviewedBy" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="LastPreviewTimeLookup" ma:index="59" nillable="true" ma:displayName="Last Previewed Date" ma:default="" ma:list="{4D83B164-8C00-474C-8363-38E0B8FF22E3}" ma:internalName="LastPreviewTimeLookup" ma:readOnly="true" ma:showField="LastPreviewTime" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="LastPreviewVersionLookup" ma:index="60" nillable="true" ma:displayName="Last Previewed Version" ma:default="" ma:list="{4D83B164-8C00-474C-8363-38E0B8FF22E3}" ma:internalName="LastPreviewVersionLookup" ma:readOnly="true" ma:showField="LastPreviewVersion" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="LastPublishErrorLookup" ma:index="61" nillable="true" ma:displayName="Last Publish Attempt Error" ma:default="" ma:list="{4D83B164-8C00-474C-8363-38E0B8FF22E3}" ma:internalName="LastPublishErrorLookup" ma:readOnly="true" ma:showField="LastPublishError" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="LastPublishResultLookup" ma:index="62" nillable="true" ma:displayName="Last Publish Attempt Result" ma:default="" ma:list="{4D83B164-8C00-474C-8363-38E0B8FF22E3}" ma:internalName="LastPublishResultLookup" ma:readOnly="true" ma:showField="LastPublishResult" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="LastPublishAttemptDateLookup" ma:index="63" nillable="true" ma:displayName="Last Publish Attempted On" ma:default="" ma:list="{4D83B164-8C00-474C-8363-38E0B8FF22E3}" ma:internalName="LastPublishAttemptDateLookup" ma:readOnly="true" ma:showField="LastPublishAttemptDate" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="LastPublishedByLookup" ma:index="64" nillable="true" ma:displayName="Last Published By" ma:default="" ma:list="{4D83B164-8C00-474C-8363-38E0B8FF22E3}" ma:internalName="LastPublishedByLookup" ma:readOnly="true" ma:showField="LastPublishedBy" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="LastPublishTimeLookup" ma:index="65" nillable="true" ma:displayName="Last Published Date" ma:default="" ma:list="{4D83B164-8C00-474C-8363-38E0B8FF22E3}" ma:internalName="LastPublishTimeLookup" ma:readOnly="true" ma:showField="LastPublishTime" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="LastPublishVersionLookup" ma:index="66" nillable="true" ma:displayName="Last Published Version" ma:default="" ma:list="{4D83B164-8C00-474C-8363-38E0B8FF22E3}" ma:internalName="LastPublishVersionLookup" ma:readOnly="true" ma:showField="LastPublishVersion" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="TPLaunchHelpLinkType" ma:index="67" nillable="true" ma:displayName="Launch Help Link Type" ma:default="Template" ma:internalName="TPLaunchHelpLinkType">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Choice">
-          <xsd:enumeration value="Template"/>
-          <xsd:enumeration value="Training"/>
-          <xsd:enumeration value="URL"/>
-          <xsd:enumeration value="None"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="LegacyData" ma:index="68" nillable="true" ma:displayName="Legacy Data" ma:default="" ma:internalName="LegacyData" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TPLaunchHelpLink" ma:index="69" nillable="true" ma:displayName="Link to Launch Help Topic" ma:default="" ma:internalName="TPLaunchHelpLink">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="LocComments" ma:index="70" nillable="true" ma:displayName="Loc Approval Comments" ma:default="" ma:internalName="LocComments" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="LocLastLocAttemptVersionLookup" ma:index="71" nillable="true" ma:displayName="Loc Last Loc Attempt Version" ma:default="" ma:list="{BC39992D-5589-4A4E-8B38-02E0637E5C25}" ma:internalName="LocLastLocAttemptVersionLookup" ma:readOnly="false" ma:showField="LastLocAttemptVersion" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Lookup"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="LocLastLocAttemptVersionTypeLookup" ma:index="72" nillable="true" ma:displayName="Loc Last Loc Attempt Version Type" ma:default="" ma:list="{BC39992D-5589-4A4E-8B38-02E0637E5C25}" ma:internalName="LocLastLocAttemptVersionTypeLookup" ma:readOnly="true" ma:showField="LastLocAttemptVersionType" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Lookup"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="LocManualTestRequired" ma:index="73" nillable="true" ma:displayName="Loc Manual Test Required" ma:default="" ma:internalName="LocManualTestRequired" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Boolean"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="LocMarketGroupTiers2" ma:index="74" nillable="true" ma:displayName="Loc Market Group Tiers" ma:internalName="LocMarketGroupTiers2" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="LocNewPublishedVersionLookup" ma:index="75" nillable="true" ma:displayName="Loc New Published Version Lookup" ma:default="" ma:list="{BC39992D-5589-4A4E-8B38-02E0637E5C25}" ma:internalName="LocNewPublishedVersionLookup" ma:readOnly="true" ma:showField="NewPublishedVersion" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Lookup"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="LocOverallHandbackStatusLookup" ma:index="76" nillable="true" ma:displayName="Loc Overall Handback Status" ma:default="" ma:list="{BC39992D-5589-4A4E-8B38-02E0637E5C25}" ma:internalName="LocOverallHandbackStatusLookup" ma:readOnly="true" ma:showField="OverallHandbackStatus" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Lookup"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="LocOverallLocStatusLookup" ma:index="77" nillable="true" ma:displayName="Loc Overall Localize Status" ma:default="" ma:list="{BC39992D-5589-4A4E-8B38-02E0637E5C25}" ma:internalName="LocOverallLocStatusLookup" ma:readOnly="true" ma:showField="OverallLocStatus" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Lookup"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="LocOverallPreviewStatusLookup" ma:index="78" nillable="true" ma:displayName="Loc Overall Preview Status" ma:default="" ma:list="{BC39992D-5589-4A4E-8B38-02E0637E5C25}" ma:internalName="LocOverallPreviewStatusLookup" ma:readOnly="true" ma:showField="OverallPreviewStatus" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Lookup"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="LocOverallPublishStatusLookup" ma:index="79" nillable="true" ma:displayName="Loc Overall Publish Status" ma:default="" ma:list="{BC39992D-5589-4A4E-8B38-02E0637E5C25}" ma:internalName="LocOverallPublishStatusLookup" ma:readOnly="true" ma:showField="OverallPublishStatus" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Lookup"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="IntlLocPriority" ma:index="80" nillable="true" ma:displayName="Loc Priority" ma:default="" ma:internalName="IntlLocPriority" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="LocProcessedForHandoffsLookup" ma:index="81" nillable="true" ma:displayName="Loc Processed For Handoffs" ma:default="" ma:list="{BC39992D-5589-4A4E-8B38-02E0637E5C25}" ma:internalName="LocProcessedForHandoffsLookup" ma:readOnly="true" ma:showField="ProcessedForHandoffs" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Lookup"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="LocProcessedForMarketsLookup" ma:index="82" nillable="true" ma:displayName="Loc Processed For Markets" ma:default="" ma:list="{BC39992D-5589-4A4E-8B38-02E0637E5C25}" ma:internalName="LocProcessedForMarketsLookup" ma:readOnly="true" ma:showField="ProcessedForMarkets" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Lookup"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="LocPublishedDependentAssetsLookup" ma:index="83" nillable="true" ma:displayName="Loc Published Dependent Assets" ma:default="" ma:list="{BC39992D-5589-4A4E-8B38-02E0637E5C25}" ma:internalName="LocPublishedDependentAssetsLookup" ma:readOnly="true" ma:showField="PublishedDependentAssets" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Lookup"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="LocPublishedLinkedAssetsLookup" ma:index="84" nillable="true" ma:displayName="Loc Published Linked Assets" ma:default="" ma:list="{BC39992D-5589-4A4E-8B38-02E0637E5C25}" ma:internalName="LocPublishedLinkedAssetsLookup" ma:readOnly="true" ma:showField="PublishedLinkedAssets" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Lookup"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="LocRecommendedHandoff" ma:index="85" nillable="true" ma:displayName="Loc Recommended Handoff" ma:default="" ma:indexed="true" ma:internalName="LocRecommendedHandoff" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="LocalizationTagsTaxHTField0" ma:index="87" nillable="true" ma:taxonomy="true" ma:internalName="LocalizationTagsTaxHTField0" ma:taxonomyFieldName="LocalizationTags" ma:displayName="Localization Tags" ma:readOnly="false" ma:default="" ma:fieldId="{28ca5b26-415b-4822-b35b-d9a845b1b83b}" ma:taxonomyMulti="true" ma:sspId="8f79753a-75d3-41f5-8ca3-40b843941b4f" ma:termSetId="5b7703a5-8e8b-4b58-8b31-1cea35331da3" ma:anchorId="00000000-0000-0000-0000-000000000000" ma:open="false" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MachineTranslated" ma:index="88" nillable="true" ma:displayName="Machine Translated" ma:default="" ma:internalName="MachineTranslated" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Boolean"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Manager" ma:index="89" nillable="true" ma:displayName="Manager" ma:hidden="true" ma:internalName="Manager" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Markets" ma:index="90" nillable="true" ma:displayName="Markets" ma:default="" ma:description="Leave blank to show in all markets" ma:list="{388FC2BA-F530-4FF7-911A-621CAE6AFBD3}" ma:internalName="Markets" ma:readOnly="false" ma:showField="MarketName" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="Milestone" ma:index="91" nillable="true" ma:displayName="Milestone" ma:default="" ma:internalName="Milestone" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TPNamespace" ma:index="94" nillable="true" ma:displayName="Namespace" ma:default="" ma:internalName="TPNamespace">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="NumericId" ma:index="95" nillable="true" ma:displayName="Numeric ID" ma:default="" ma:indexed="true" ma:internalName="NumericId" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Number"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="NumOfRatingsLookup" ma:index="96" nillable="true" ma:displayName="NumOfRatings" ma:default="" ma:list="{4D83B164-8C00-474C-8363-38E0B8FF22E3}" ma:internalName="NumOfRatingsLookup" ma:readOnly="true" ma:showField="NumOfRatings" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="OOCacheId" ma:index="97" nillable="true" ma:displayName="OOCacheId" ma:internalName="OOCacheId" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="OpenTemplate" ma:index="98" nillable="true" ma:displayName="Open Template" ma:default="true" ma:internalName="OpenTemplate">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Boolean"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="OriginAsset" ma:index="99" nillable="true" ma:displayName="Origin Asset" ma:default="" ma:internalName="OriginAsset" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="OriginalRelease" ma:index="100" nillable="true" ma:displayName="Original Release" ma:default="15" ma:internalName="OriginalRelease" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Choice">
-          <xsd:enumeration value="14"/>
-          <xsd:enumeration value="15"/>
-          <xsd:enumeration value="16"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="OriginalSourceMarket" ma:index="101" nillable="true" ma:displayName="Original Source Market Group" ma:default="" ma:internalName="OriginalSourceMarket" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="OutputCachingOn" ma:index="102" nillable="true" ma:displayName="Output Caching" ma:default="true" ma:hidden="true" ma:internalName="OutputCachingOn" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Boolean"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="ParentAssetId" ma:index="103" nillable="true" ma:displayName="Parent Asset Id" ma:default="" ma:internalName="ParentAssetId" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="PlannedPubDate" ma:index="104" nillable="true" ma:displayName="Planned Publish Date" ma:default="" ma:indexed="true" ma:internalName="PlannedPubDate" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:DateTime"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="PolicheckWords" ma:index="105" nillable="true" ma:displayName="Policheck Words" ma:default="" ma:internalName="PolicheckWords" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="BusinessGroup" ma:index="106" nillable="true" ma:displayName="Product Division Owner" ma:default="" ma:internalName="BusinessGroup" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="UAProjectedTotalWords" ma:index="107" nillable="true" ma:displayName="Projected Word Count" ma:default="" ma:internalName="UAProjectedTotalWords" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Provider" ma:index="108" nillable="true" ma:displayName="Provider" ma:default="" ma:internalName="Provider" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Providers" ma:index="109" nillable="true" ma:displayName="Providers" ma:default="" ma:internalName="Providers">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="PublishStatusLookup" ma:index="110" nillable="true" ma:displayName="Publish Status" ma:default="" ma:list="{4D83B164-8C00-474C-8363-38E0B8FF22E3}" ma:internalName="PublishStatusLookup" ma:readOnly="false" ma:showField="PublishStatus" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="PublishTargets" ma:index="111" nillable="true" ma:displayName="Publish Target" ma:default="OfficeOnlineVNext" ma:internalName="PublishTargets" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="RecommendationsModifier" ma:index="112" nillable="true" ma:displayName="Recommendations Modifier" ma:default="" ma:internalName="RecommendationsModifier" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Number"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="ArtSampleDocs" ma:index="113" nillable="true" ma:displayName="Sample Docs" ma:default="" ma:hidden="true" ma:internalName="ArtSampleDocs" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="ScenarioTagsTaxHTField0" ma:index="115" nillable="true" ma:taxonomy="true" ma:internalName="ScenarioTagsTaxHTField0" ma:taxonomyFieldName="ScenarioTags" ma:displayName="Scenarios" ma:readOnly="false" ma:default="" ma:fieldId="{1c8e7b99-44ca-46c8-84b8-12cd8d7cf8ee}" ma:taxonomyMulti="true" ma:sspId="8f79753a-75d3-41f5-8ca3-40b843941b4f" ma:termSetId="4b7d5f16-e2f2-4fc0-bab3-6e8b931e57d6" ma:anchorId="00000000-0000-0000-0000-000000000000" ma:open="false" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="ShowIn" ma:index="117" nillable="true" ma:displayName="Show In" ma:default="Show everywhere" ma:internalName="ShowIn" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Choice">
-          <xsd:enumeration value="Hide on web"/>
-          <xsd:enumeration value="On Web no search"/>
-          <xsd:enumeration value="Show everywhere"/>
-          <xsd:enumeration value="Special use only"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="SourceTitle" ma:index="118" nillable="true" ma:displayName="Source Title" ma:default="" ma:indexed="true" ma:internalName="SourceTitle" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="CSXSubmissionDate" ma:index="119" nillable="true" ma:displayName="Submission Date" ma:default="" ma:internalName="CSXSubmissionDate" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:DateTime"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="SubmitterId" ma:index="120" nillable="true" ma:displayName="Submitter ID" ma:default="" ma:internalName="SubmitterId" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="121" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c59171da-55f1-4c8b-8421-0d1d3f99d741}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAllLabel" ma:index="122" nillable="true" ma:displayName="Taxonomy Catch All Column1" ma:hidden="true" ma:list="{c59171da-55f1-4c8b-8421-0d1d3f99d741}" ma:internalName="TaxCatchAllLabel" ma:readOnly="true" ma:showField="CatchAllDataLabel" ma:web="1119c2e5-8fb9-4d5f-baf1-202c530f2c34">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="TemplateStatus" ma:index="123" nillable="true" ma:displayName="Template Status" ma:default="" ma:internalName="TemplateStatus">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TemplateTemplateType" ma:index="124" nillable="true" ma:displayName="Template Type" ma:default="" ma:internalName="TemplateTemplateType">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="ThumbnailAssetId" ma:index="125" nillable="true" ma:displayName="Thumbnail Image Asset" ma:default="" ma:internalName="ThumbnailAssetId" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TimesCloned" ma:index="126" nillable="true" ma:displayName="Times Cloned" ma:default="" ma:internalName="TimesCloned" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Number"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TrustLevel" ma:index="128" nillable="true" ma:displayName="Trust Level" ma:default="1 Microsoft Managed Content" ma:internalName="TrustLevel" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="UALocComments" ma:index="129" nillable="true" ma:displayName="UA Loc Comments" ma:default="" ma:internalName="UALocComments" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="UALocRecommendation" ma:index="130" nillable="true" ma:displayName="UA Loc Recommendation" ma:default="Localize" ma:internalName="UALocRecommendation" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Choice">
-          <xsd:enumeration value="Localize"/>
-          <xsd:enumeration value="Never Localize"/>
-          <xsd:enumeration value="Priority Localize"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="UANotes" ma:index="131" nillable="true" ma:displayName="UA Notes" ma:default="" ma:internalName="UANotes" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TPAppVersion" ma:index="132" nillable="true" ma:displayName="Version" ma:default="" ma:internalName="TPAppVersion">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="VoteCount" ma:index="133" nillable="true" ma:displayName="Vote Count" ma:default="" ma:internalName="VoteCount" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="22" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="127" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9659279B-CA79-44FF-BF15-83F6AAD0C4E7}">
   <ds:schemaRefs>
@@ -5077,16 +5072,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2B99CB1-8E2B-4A06-BE97-F0CCC71A7538}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1119c2e5-8fb9-4d5f-baf1-202c530f2c34"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE70CA04-6118-4D7D-973A-6229EC59A34E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5102,4 +5087,14 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2B99CB1-8E2B-4A06-BE97-F0CCC71A7538}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1119c2e5-8fb9-4d5f-baf1-202c530f2c34"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>